--- a/database/event/3313/event_3313_evp_summary.xlsx
+++ b/database/event/3313/event_3313_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.8023</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0302</v>
+        <v>1.9738</v>
       </c>
       <c r="E2" t="n">
         <v>6.0685</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6811</v>
+        <v>4.8216</v>
       </c>
       <c r="C3" t="n">
-        <v>1.3902</v>
+        <v>1.432</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4697</v>
+        <v>1.477</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6811</v>
+        <v>4.8216</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2053</v>
+        <v>4.3458</v>
       </c>
       <c r="G3" t="n">
         <v>0.4758</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3585</v>
+        <v>4.9237</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5327</v>
+        <v>3.9908</v>
       </c>
       <c r="J3" t="n">
         <v>0.4758</v>
@@ -575,7 +575,7 @@
         <v>156</v>
       </c>
       <c r="M3" t="n">
-        <v>4.0085</v>
+        <v>4.4666</v>
       </c>
       <c r="N3" t="n">
         <v>264</v>
@@ -594,7 +594,7 @@
         <v>1.3154</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3679</v>
+        <v>1.3206</v>
       </c>
       <c r="E4" t="n">
         <v>4.4291</v>
@@ -640,7 +640,7 @@
         <v>1.2992</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3459</v>
+        <v>1.299</v>
       </c>
       <c r="E5" t="n">
         <v>4.3747</v>
@@ -686,7 +686,7 @@
         <v>1.1618</v>
       </c>
       <c r="D6" t="n">
-        <v>1.159</v>
+        <v>1.1146</v>
       </c>
       <c r="E6" t="n">
         <v>3.9119</v>
@@ -732,7 +732,7 @@
         <v>0.9298999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8435</v>
+        <v>0.8035</v>
       </c>
       <c r="E7" t="n">
         <v>3.131</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.3319</v>
+        <v>2.8926</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6925</v>
+        <v>0.8591</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.7085</v>
       </c>
       <c r="E8" t="n">
-        <v>2.3319</v>
+        <v>2.8926</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1364</v>
+        <v>2.6971</v>
       </c>
       <c r="G8" t="n">
         <v>0.1955</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1364</v>
+        <v>2.6971</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7316</v>
+        <v>2.1861</v>
       </c>
       <c r="J8" t="n">
         <v>0.1955</v>
@@ -805,7 +805,7 @@
         <v>76</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9271</v>
+        <v>2.3816</v>
       </c>
       <c r="N8" t="n">
         <v>132</v>
@@ -814,127 +814,127 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1927</v>
+        <v>2.2212</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6512</v>
+        <v>0.6597</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4644</v>
+        <v>0.441</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1927</v>
+        <v>2.2212</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5508</v>
+        <v>2.0838</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6419</v>
+        <v>0.1374</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5508</v>
+        <v>2.0838</v>
       </c>
       <c r="I9" t="n">
-        <v>1.257</v>
+        <v>1.689</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6419</v>
+        <v>0.1374</v>
       </c>
       <c r="K9" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="L9" t="n">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8989</v>
+        <v>1.8264</v>
       </c>
       <c r="N9" t="n">
-        <v>264</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9385</v>
+        <v>2.1927</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5757</v>
+        <v>0.6512</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3617</v>
+        <v>0.4297</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9385</v>
+        <v>2.1927</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8011</v>
+        <v>1.5508</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1374</v>
+        <v>0.6419</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8011</v>
+        <v>1.5508</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4598</v>
+        <v>1.257</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1374</v>
+        <v>0.6419</v>
       </c>
       <c r="K10" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="L10" t="n">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="M10" t="n">
-        <v>1.5972</v>
+        <v>1.8989</v>
       </c>
       <c r="N10" t="n">
-        <v>132</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.6602</v>
+        <v>2.0708</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4931</v>
+        <v>0.615</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2493</v>
+        <v>0.3811</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6602</v>
+        <v>2.0708</v>
       </c>
       <c r="F11" t="n">
-        <v>2.1216</v>
+        <v>2.5306</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4614</v>
+        <v>-0.4598</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1216</v>
+        <v>2.5306</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7196</v>
+        <v>2.0511</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4614</v>
+        <v>-0.4598</v>
       </c>
       <c r="K11" t="n">
         <v>46</v>
@@ -943,7 +943,7 @@
         <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>1.2582</v>
+        <v>1.5913</v>
       </c>
       <c r="N11" t="n">
         <v>96</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5056</v>
+        <v>2.0423</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4471</v>
+        <v>0.6065</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1869</v>
+        <v>0.3697</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5056</v>
+        <v>2.0423</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9654</v>
+        <v>2.5037</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4598</v>
+        <v>-0.4614</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9654</v>
+        <v>2.5037</v>
       </c>
       <c r="I12" t="n">
-        <v>1.593</v>
+        <v>2.0293</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4598</v>
+        <v>-0.4614</v>
       </c>
       <c r="K12" t="n">
         <v>46</v>
@@ -989,7 +989,7 @@
         <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1332</v>
+        <v>1.5679</v>
       </c>
       <c r="N12" t="n">
         <v>96</v>
@@ -998,139 +998,139 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4959</v>
+        <v>1.5078</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4443</v>
+        <v>0.4478</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1829</v>
+        <v>0.1568</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4959</v>
+        <v>1.5078</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1305</v>
+        <v>2.5078</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3654</v>
+        <v>-1</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1305</v>
+        <v>2.5078</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9163</v>
+        <v>2.0327</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3654</v>
+        <v>-1</v>
       </c>
       <c r="K13" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L13" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2817</v>
+        <v>1.0327</v>
       </c>
       <c r="N13" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.2036</v>
+        <v>1.4959</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3575</v>
+        <v>0.4443</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0649</v>
+        <v>0.1521</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2036</v>
+        <v>1.4959</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2036</v>
+        <v>1.1305</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.3654</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2036</v>
+        <v>1.1305</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2036</v>
+        <v>0.9163</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.3654</v>
       </c>
       <c r="K14" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2036</v>
+        <v>1.2817</v>
       </c>
       <c r="N14" t="n">
-        <v>89</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9703000000000001</v>
+        <v>1.3099</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2882</v>
+        <v>0.389</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0294</v>
+        <v>0.078</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9703000000000001</v>
+        <v>1.3099</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9703</v>
+        <v>1.3099</v>
       </c>
       <c r="G15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9703</v>
+        <v>1.3099</v>
       </c>
       <c r="I15" t="n">
-        <v>1.597</v>
+        <v>1.3099</v>
       </c>
       <c r="J15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="L15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.597</v>
+        <v>1.3099</v>
       </c>
       <c r="N15" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9392</v>
+        <v>1.1425</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2789</v>
+        <v>0.3393</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0419</v>
+        <v>0.0113</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9392</v>
+        <v>1.1425</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8368</v>
+        <v>1.0401</v>
       </c>
       <c r="G16" t="n">
         <v>0.1024</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8368</v>
+        <v>1.0401</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6783</v>
+        <v>0.843</v>
       </c>
       <c r="J16" t="n">
         <v>0.1024</v>
@@ -1173,7 +1173,7 @@
         <v>50</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7807000000000001</v>
+        <v>0.9454</v>
       </c>
       <c r="N16" t="n">
         <v>96</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8457</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2512</v>
+        <v>0.2965</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.0461</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8457</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8454</v>
+        <v>1.9982</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9997</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8454</v>
+        <v>1.9982</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4957</v>
+        <v>1.6196</v>
       </c>
       <c r="J17" t="n">
         <v>-0.9997</v>
@@ -1219,7 +1219,7 @@
         <v>76</v>
       </c>
       <c r="M17" t="n">
-        <v>0.496</v>
+        <v>0.6198999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>132</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5942</v>
+        <v>0.6317</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1765</v>
+        <v>0.1876</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1813</v>
+        <v>-0.1922</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5942</v>
+        <v>0.6317</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4281</v>
+        <v>0.6317</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0223</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4281</v>
+        <v>0.6317</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.347</v>
+        <v>0.6317</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0223</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="L18" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6753</v>
+        <v>0.6317</v>
       </c>
       <c r="N18" t="n">
-        <v>264</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4408</v>
+        <v>0.5942</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1309</v>
+        <v>0.1765</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2433</v>
+        <v>-0.2072</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4408</v>
+        <v>0.5942</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4408</v>
+        <v>-0.4281</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1.0223</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4408</v>
+        <v>-0.4281</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4408</v>
+        <v>-0.347</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.0223</v>
       </c>
       <c r="K19" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4408</v>
+        <v>0.6753</v>
       </c>
       <c r="N19" t="n">
-        <v>89</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20">
@@ -1330,7 +1330,7 @@
         <v>0.125</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2513</v>
+        <v>-0.2762</v>
       </c>
       <c r="E20" t="n">
         <v>0.421</v>
@@ -1376,7 +1376,7 @@
         <v>0.1241</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2526</v>
+        <v>-0.2775</v>
       </c>
       <c r="E21" t="n">
         <v>0.4177</v>
@@ -1422,7 +1422,7 @@
         <v>0.1126</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2682</v>
+        <v>-0.2929</v>
       </c>
       <c r="E22" t="n">
         <v>0.3791</v>
@@ -1458,691 +1458,691 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2092</v>
+        <v>0.334</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0621</v>
+        <v>0.0992</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3369</v>
+        <v>-0.3108</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2092</v>
+        <v>0.334</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2092</v>
+        <v>0.334</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2092</v>
+        <v>0.334</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2092</v>
+        <v>0.334</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2092</v>
+        <v>0.334</v>
       </c>
       <c r="N23" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1891</v>
+        <v>0.2092</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0562</v>
+        <v>0.0621</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.345</v>
+        <v>-0.3606</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1891</v>
+        <v>0.2092</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1891</v>
+        <v>0.2092</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1891</v>
+        <v>0.2092</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1891</v>
+        <v>0.2092</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1891</v>
+        <v>0.2092</v>
       </c>
       <c r="N24" t="n">
-        <v>72</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1014</v>
+        <v>0.1891</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0301</v>
+        <v>0.0562</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3804</v>
+        <v>-0.3686</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1014</v>
+        <v>0.1891</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1014</v>
+        <v>0.1891</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1014</v>
+        <v>0.1891</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1014</v>
+        <v>0.1891</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1014</v>
+        <v>0.1891</v>
       </c>
       <c r="N25" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0284</v>
+        <v>0.0301</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3827</v>
+        <v>-0.4035</v>
       </c>
       <c r="E26" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="F26" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.1014</v>
       </c>
       <c r="N26" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0299</v>
+        <v>0.0552</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0089</v>
+        <v>0.0164</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4334</v>
+        <v>-0.4219</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0299</v>
+        <v>0.0552</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0299</v>
+        <v>0.569</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.5138</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0299</v>
+        <v>0.569</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0299</v>
+        <v>0.4612</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.5138</v>
       </c>
       <c r="K27" t="n">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0299</v>
+        <v>-0.05260000000000004</v>
       </c>
       <c r="N27" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1025</v>
+        <v>-0.0299</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0304</v>
+        <v>-0.0089</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4628</v>
+        <v>-0.4558</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1025</v>
+        <v>-0.0299</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1025</v>
+        <v>-0.0299</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1025</v>
+        <v>-0.0299</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1025</v>
+        <v>-0.0299</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1025</v>
+        <v>-0.0299</v>
       </c>
       <c r="N28" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1851</v>
+        <v>-0.0601</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.055</v>
+        <v>-0.0178</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4961</v>
+        <v>-0.4679</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1851</v>
+        <v>-0.0601</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3287</v>
+        <v>-0.0601</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5138</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3287</v>
+        <v>-0.0601</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2664</v>
+        <v>-0.0601</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5138</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="L29" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2474</v>
+        <v>-0.0601</v>
       </c>
       <c r="N29" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2363</v>
+        <v>-0.1025</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0702</v>
+        <v>-0.0304</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5168</v>
+        <v>-0.4847</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2363</v>
+        <v>-0.1025</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2363</v>
+        <v>-0.1025</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2363</v>
+        <v>-0.1025</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2363</v>
+        <v>-0.1025</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2363</v>
+        <v>-0.1025</v>
       </c>
       <c r="N30" t="n">
-        <v>89</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2559</v>
+        <v>-0.106</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.076</v>
+        <v>-0.0315</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.4861</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2559</v>
+        <v>-0.106</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2559</v>
+        <v>-0.106</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2559</v>
+        <v>-0.106</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2559</v>
+        <v>-0.106</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2559</v>
+        <v>-0.106</v>
       </c>
       <c r="N31" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.339</v>
+        <v>-0.2559</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1007</v>
+        <v>-0.076</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5583</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.339</v>
+        <v>-0.2559</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.339</v>
+        <v>-0.2559</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.339</v>
+        <v>-0.2559</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.339</v>
+        <v>-0.2559</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.339</v>
+        <v>-0.2559</v>
       </c>
       <c r="N32" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3679</v>
+        <v>-0.339</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1093</v>
+        <v>-0.1007</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.57</v>
+        <v>-0.579</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3679</v>
+        <v>-0.339</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.3032</v>
+        <v>-0.339</v>
       </c>
       <c r="G33" t="n">
-        <v>1.9353</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.3032</v>
+        <v>-0.339</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.8668</v>
+        <v>-0.339</v>
       </c>
       <c r="J33" t="n">
-        <v>1.9353</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L33" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0.06850000000000001</v>
+        <v>-0.339</v>
       </c>
       <c r="N33" t="n">
-        <v>264</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6483</v>
+        <v>-0.3679</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1925</v>
+        <v>-0.1093</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6833</v>
+        <v>-0.5905</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6483</v>
+        <v>-0.3679</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6483</v>
+        <v>-2.3032</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.9353</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6483</v>
+        <v>-2.3032</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6483</v>
+        <v>-1.8668</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1.9353</v>
       </c>
       <c r="K34" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6483</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>72</v>
+        <v>264</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8389</v>
+        <v>-0.6483</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2491</v>
+        <v>-0.1925</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7603</v>
+        <v>-0.7022</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8389</v>
+        <v>-0.6483</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.2097</v>
+        <v>-0.6483</v>
       </c>
       <c r="G35" t="n">
-        <v>0.3708</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.2097</v>
+        <v>-0.6483</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9805</v>
+        <v>-0.6483</v>
       </c>
       <c r="J35" t="n">
-        <v>0.3708</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="L35" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6097</v>
+        <v>-0.6483</v>
       </c>
       <c r="N35" t="n">
-        <v>132</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8722</v>
+        <v>-0.8389</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.259</v>
+        <v>-0.2491</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7737000000000001</v>
+        <v>-0.7781</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8722</v>
+        <v>-0.8389</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8722</v>
+        <v>-1.2097</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>0.3708</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8722</v>
+        <v>-1.2097</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8722</v>
+        <v>-0.9805</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.3708</v>
       </c>
       <c r="K36" t="n">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8722</v>
+        <v>-0.6097</v>
       </c>
       <c r="N36" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9417</v>
+        <v>-0.8722</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2797</v>
+        <v>-0.259</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8018</v>
+        <v>-0.7914</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9417</v>
+        <v>-0.8722</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9417</v>
+        <v>-0.8722</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9417</v>
+        <v>-0.8722</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9417</v>
+        <v>-0.8722</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9417</v>
+        <v>-0.8722</v>
       </c>
       <c r="N37" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38">
@@ -2158,7 +2158,7 @@
         <v>-0.3227</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8603</v>
+        <v>-0.8768</v>
       </c>
       <c r="E38" t="n">
         <v>-1.0865</v>
@@ -2204,7 +2204,7 @@
         <v>-0.4327</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.01</v>
+        <v>-1.0244</v>
       </c>
       <c r="E39" t="n">
         <v>-1.457</v>
@@ -2250,7 +2250,7 @@
         <v>-0.434</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0118</v>
+        <v>-1.0262</v>
       </c>
       <c r="E40" t="n">
         <v>-1.4615</v>
@@ -2296,7 +2296,7 @@
         <v>-0.547</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1654</v>
+        <v>-1.1777</v>
       </c>
       <c r="E41" t="n">
         <v>-1.8419</v>

--- a/database/event/3313/event_3313_evp_summary.xlsx
+++ b/database/event/3313/event_3313_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0685</v>
+        <v>6.0324</v>
       </c>
       <c r="C2" t="n">
-        <v>1.8023</v>
+        <v>1.7915</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9738</v>
+        <v>2.0853</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0685</v>
+        <v>6.0324</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1124</v>
+        <v>2.5004</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9561</v>
+        <v>3.532</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1124</v>
+        <v>3.3236</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7121</v>
+        <v>1.7281</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9561</v>
+        <v>3.532</v>
       </c>
       <c r="K2" t="n">
         <v>108</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>5.668200000000001</v>
+        <v>5.2601</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -538,127 +538,127 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>suNny</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.8216</v>
+        <v>5.24</v>
       </c>
       <c r="C3" t="n">
-        <v>1.432</v>
+        <v>1.5562</v>
       </c>
       <c r="D3" t="n">
-        <v>1.477</v>
+        <v>1.7276</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8216</v>
+        <v>5.24</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3458</v>
+        <v>2.359</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4758</v>
+        <v>2.881</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9237</v>
+        <v>2.8252</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9908</v>
+        <v>1.469</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4758</v>
+        <v>2.881</v>
       </c>
       <c r="K3" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L3" t="n">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4666</v>
+        <v>4.35</v>
       </c>
       <c r="N3" t="n">
-        <v>264</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>oskar</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4291</v>
+        <v>4.3879</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3154</v>
+        <v>1.3031</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3206</v>
+        <v>1.3429</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4291</v>
+        <v>4.3879</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4267</v>
+        <v>3.7391</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0024</v>
+        <v>0.6488</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4267</v>
+        <v>7.688</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7774</v>
+        <v>3.9974</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0024</v>
+        <v>0.6488</v>
       </c>
       <c r="K4" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L4" t="n">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7798</v>
+        <v>4.6462</v>
       </c>
       <c r="N4" t="n">
-        <v>297</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>suNny</t>
+          <t>oskar</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3747</v>
+        <v>4.2217</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2992</v>
+        <v>1.2538</v>
       </c>
       <c r="D5" t="n">
-        <v>1.299</v>
+        <v>1.2679</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3747</v>
+        <v>4.2217</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3134</v>
+        <v>3.1639</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0613</v>
+        <v>1.0578</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3134</v>
+        <v>5.6613</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0646</v>
+        <v>2.9436</v>
       </c>
       <c r="J5" t="n">
-        <v>3.0613</v>
+        <v>1.0578</v>
       </c>
       <c r="K5" t="n">
         <v>115</v>
@@ -667,7 +667,7 @@
         <v>182</v>
       </c>
       <c r="M5" t="n">
-        <v>4.1259</v>
+        <v>4.0014</v>
       </c>
       <c r="N5" t="n">
         <v>297</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9119</v>
+        <v>3.9236</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1618</v>
+        <v>1.1653</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1146</v>
+        <v>1.1333</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9119</v>
+        <v>3.9236</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1821</v>
+        <v>3.166</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7298</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1821</v>
+        <v>5.6688</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5792</v>
+        <v>2.9475</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7298</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>115</v>
@@ -713,7 +713,7 @@
         <v>182</v>
       </c>
       <c r="M6" t="n">
-        <v>3.309</v>
+        <v>3.7051</v>
       </c>
       <c r="N6" t="n">
         <v>297</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.131</v>
+        <v>3.3526</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9957</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8035</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>3.131</v>
+        <v>3.3526</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2364</v>
+        <v>3.2306</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1054</v>
+        <v>0.122</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2364</v>
+        <v>5.8963</v>
       </c>
       <c r="I7" t="n">
-        <v>2.6232</v>
+        <v>3.0658</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1054</v>
+        <v>0.122</v>
       </c>
       <c r="K7" t="n">
         <v>115</v>
@@ -759,7 +759,7 @@
         <v>182</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5178</v>
+        <v>3.1878</v>
       </c>
       <c r="N7" t="n">
         <v>297</v>
@@ -768,81 +768,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RUBINO</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.8926</v>
+        <v>3.3348</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8591</v>
+        <v>0.9903999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7085</v>
+        <v>0.8675</v>
       </c>
       <c r="E8" t="n">
-        <v>2.8926</v>
+        <v>3.3348</v>
       </c>
       <c r="F8" t="n">
-        <v>2.6971</v>
+        <v>2.4381</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1955</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6971</v>
+        <v>3.1039</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1861</v>
+        <v>1.6139</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1955</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="L8" t="n">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="M8" t="n">
-        <v>2.3816</v>
+        <v>2.5106</v>
       </c>
       <c r="N8" t="n">
-        <v>132</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>RUBINO</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2212</v>
+        <v>2.8402</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6597</v>
+        <v>0.8435</v>
       </c>
       <c r="D9" t="n">
-        <v>0.441</v>
+        <v>0.6442</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2212</v>
+        <v>2.8402</v>
       </c>
       <c r="F9" t="n">
-        <v>2.0838</v>
+        <v>2.6615</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1374</v>
+        <v>0.1787</v>
       </c>
       <c r="H9" t="n">
-        <v>2.0838</v>
+        <v>3.891</v>
       </c>
       <c r="I9" t="n">
-        <v>1.689</v>
+        <v>2.0231</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1374</v>
+        <v>0.1787</v>
       </c>
       <c r="K9" t="n">
         <v>56</v>
@@ -851,7 +851,7 @@
         <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8264</v>
+        <v>2.2018</v>
       </c>
       <c r="N9" t="n">
         <v>132</v>
@@ -860,81 +860,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.1927</v>
+        <v>2.6703</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6512</v>
+        <v>0.793</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4297</v>
+        <v>0.5675</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1927</v>
+        <v>2.6703</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5508</v>
+        <v>2.4819</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6419</v>
+        <v>0.1884</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5508</v>
+        <v>3.2584</v>
       </c>
       <c r="I10" t="n">
-        <v>1.257</v>
+        <v>1.6942</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6419</v>
+        <v>0.1884</v>
       </c>
       <c r="K10" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="L10" t="n">
-        <v>156</v>
+        <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8989</v>
+        <v>1.8826</v>
       </c>
       <c r="N10" t="n">
-        <v>264</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.0708</v>
+        <v>2.3529</v>
       </c>
       <c r="C11" t="n">
-        <v>0.615</v>
+        <v>0.6988</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3811</v>
+        <v>0.4242</v>
       </c>
       <c r="E11" t="n">
-        <v>2.0708</v>
+        <v>2.3529</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5306</v>
+        <v>2.6888</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4598</v>
+        <v>-0.3359</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5306</v>
+        <v>3.9875</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0511</v>
+        <v>2.0733</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4598</v>
+        <v>-0.3359</v>
       </c>
       <c r="K11" t="n">
         <v>46</v>
@@ -943,7 +943,7 @@
         <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5913</v>
+        <v>1.7374</v>
       </c>
       <c r="N11" t="n">
         <v>96</v>
@@ -952,81 +952,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0423</v>
+        <v>2.3269</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6065</v>
+        <v>0.6911</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3697</v>
+        <v>0.4125</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0423</v>
+        <v>2.3269</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5037</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4614</v>
+        <v>0.3069</v>
       </c>
       <c r="H12" t="n">
-        <v>2.5037</v>
+        <v>2.02</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0293</v>
+        <v>1.0503</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4614</v>
+        <v>0.3069</v>
       </c>
       <c r="K12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L12" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5679</v>
+        <v>1.3572</v>
       </c>
       <c r="N12" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.5078</v>
+        <v>2.2677</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4478</v>
+        <v>0.6735</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1568</v>
+        <v>0.3857</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5078</v>
+        <v>2.2677</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5078</v>
+        <v>2.609</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>-0.3413</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5078</v>
+        <v>3.7062</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0327</v>
+        <v>1.9271</v>
       </c>
       <c r="J13" t="n">
-        <v>-1</v>
+        <v>-0.3413</v>
       </c>
       <c r="K13" t="n">
         <v>46</v>
@@ -1035,7 +1035,7 @@
         <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0327</v>
+        <v>1.5858</v>
       </c>
       <c r="N13" t="n">
         <v>96</v>
@@ -1044,415 +1044,415 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4959</v>
+        <v>2.143</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4443</v>
+        <v>0.6364</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1521</v>
+        <v>0.3294</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4959</v>
+        <v>2.143</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1305</v>
+        <v>1.9029</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3654</v>
+        <v>0.2401</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1305</v>
+        <v>1.9029</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9163</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3654</v>
+        <v>0.2401</v>
       </c>
       <c r="K14" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L14" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2817</v>
+        <v>1.2295</v>
       </c>
       <c r="N14" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.3099</v>
+        <v>1.9088</v>
       </c>
       <c r="C15" t="n">
-        <v>0.389</v>
+        <v>0.5669</v>
       </c>
       <c r="D15" t="n">
-        <v>0.078</v>
+        <v>0.2237</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3099</v>
+        <v>1.9088</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3099</v>
+        <v>2.6109</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3099</v>
+        <v>3.713</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3099</v>
+        <v>1.9306</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3099</v>
+        <v>1.2285</v>
       </c>
       <c r="N15" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1425</v>
+        <v>1.8428</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3393</v>
+        <v>0.5473</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0113</v>
+        <v>0.1939</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1425</v>
+        <v>1.8428</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0401</v>
+        <v>2.4595</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1024</v>
+        <v>-0.6167</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0401</v>
+        <v>3.1793</v>
       </c>
       <c r="I16" t="n">
-        <v>0.843</v>
+        <v>1.6531</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1024</v>
+        <v>-0.6167</v>
       </c>
       <c r="K16" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L16" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9454</v>
+        <v>1.0364</v>
       </c>
       <c r="N16" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.5528</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2965</v>
+        <v>0.4612</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0461</v>
+        <v>0.063</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9985000000000001</v>
+        <v>1.5528</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9982</v>
+        <v>1.5528</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9997</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9982</v>
+        <v>1.5528</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6196</v>
+        <v>1.5528</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9997</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="L17" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6198999999999999</v>
+        <v>1.5528</v>
       </c>
       <c r="N17" t="n">
-        <v>132</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>GuardiaN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6317</v>
+        <v>1.0021</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1876</v>
+        <v>0.2976</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1922</v>
+        <v>-0.1856</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6317</v>
+        <v>1.0021</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6317</v>
+        <v>-0.2194</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.2215</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6317</v>
+        <v>-0.2194</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6317</v>
+        <v>-0.1141</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.2215</v>
       </c>
       <c r="K18" t="n">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6317</v>
+        <v>1.1074</v>
       </c>
       <c r="N18" t="n">
-        <v>89</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GuardiaN</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5942</v>
+        <v>1.0002</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1765</v>
+        <v>0.297</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2072</v>
+        <v>-0.1865</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5942</v>
+        <v>1.0002</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4281</v>
+        <v>1.0002</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0223</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4281</v>
+        <v>1.0002</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.347</v>
+        <v>1.0002</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0223</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="L19" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6753</v>
+        <v>1.0002</v>
       </c>
       <c r="N19" t="n">
-        <v>264</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.421</v>
+        <v>0.8028</v>
       </c>
       <c r="C20" t="n">
-        <v>0.125</v>
+        <v>0.2384</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2762</v>
+        <v>-0.2756</v>
       </c>
       <c r="E20" t="n">
-        <v>0.421</v>
+        <v>0.8028</v>
       </c>
       <c r="F20" t="n">
-        <v>0.421</v>
+        <v>1.073</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.2702</v>
       </c>
       <c r="H20" t="n">
-        <v>0.421</v>
+        <v>1.073</v>
       </c>
       <c r="I20" t="n">
-        <v>0.421</v>
+        <v>0.5579</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.2702</v>
       </c>
       <c r="K20" t="n">
-        <v>134</v>
+        <v>46</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>0.421</v>
+        <v>0.2877</v>
       </c>
       <c r="N20" t="n">
-        <v>134</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4177</v>
+        <v>0.7463</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1241</v>
+        <v>0.2216</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2775</v>
+        <v>-0.3011</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4177</v>
+        <v>0.7463</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4177</v>
+        <v>0.7463</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4177</v>
+        <v>0.7463</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4177</v>
+        <v>0.7463</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4177</v>
+        <v>0.7463</v>
       </c>
       <c r="N21" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.3791</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1126</v>
+        <v>0.1858</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2929</v>
+        <v>-0.3556</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3791</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3791</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3791</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3791</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3791</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>134</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23">
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.334</v>
+        <v>0.5869</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0992</v>
+        <v>0.1743</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3108</v>
+        <v>-0.3731</v>
       </c>
       <c r="E23" t="n">
-        <v>0.334</v>
+        <v>0.5869</v>
       </c>
       <c r="F23" t="n">
-        <v>0.334</v>
+        <v>0.5869</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.334</v>
+        <v>0.5869</v>
       </c>
       <c r="I23" t="n">
-        <v>0.334</v>
+        <v>0.5869</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.334</v>
+        <v>0.5869</v>
       </c>
       <c r="N23" t="n">
         <v>89</v>
@@ -1504,32 +1504,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2092</v>
+        <v>0.5028</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0621</v>
+        <v>0.1493</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3606</v>
+        <v>-0.411</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2092</v>
+        <v>0.5028</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2092</v>
+        <v>0.5028</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2092</v>
+        <v>0.5028</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2092</v>
+        <v>0.5028</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2092</v>
+        <v>0.5028</v>
       </c>
       <c r="N24" t="n">
         <v>134</v>
@@ -1550,170 +1550,170 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1891</v>
+        <v>0.4055</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0562</v>
+        <v>0.1204</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3686</v>
+        <v>-0.455</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1891</v>
+        <v>0.4055</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1891</v>
+        <v>0.4055</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1891</v>
+        <v>0.4055</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1891</v>
+        <v>0.4055</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>72</v>
+        <v>134</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1891</v>
+        <v>0.4055</v>
       </c>
       <c r="N25" t="n">
-        <v>72</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1014</v>
+        <v>0.3909</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0301</v>
+        <v>0.1161</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4035</v>
+        <v>-0.4615</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1014</v>
+        <v>0.3909</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1014</v>
+        <v>0.3909</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1014</v>
+        <v>0.3909</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1014</v>
+        <v>0.3909</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1014</v>
+        <v>0.3909</v>
       </c>
       <c r="N26" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0552</v>
+        <v>0.3474</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0164</v>
+        <v>0.1032</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4219</v>
+        <v>-0.4812</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0552</v>
+        <v>0.3474</v>
       </c>
       <c r="F27" t="n">
-        <v>0.569</v>
+        <v>0.3474</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.5138</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.569</v>
+        <v>0.3474</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4612</v>
+        <v>0.3474</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.5138</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="L27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.05260000000000004</v>
+        <v>0.3474</v>
       </c>
       <c r="N27" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0299</v>
+        <v>0.2943</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0089</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4558</v>
+        <v>-0.5052</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0299</v>
+        <v>0.2943</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0299</v>
+        <v>0.2943</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0299</v>
+        <v>0.2943</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0299</v>
+        <v>0.2943</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0299</v>
+        <v>0.2943</v>
       </c>
       <c r="N28" t="n">
         <v>84</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0601</v>
+        <v>0.2415</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0178</v>
+        <v>0.0717</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4679</v>
+        <v>-0.529</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0601</v>
+        <v>0.2415</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0601</v>
+        <v>0.2415</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0601</v>
+        <v>0.2415</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0601</v>
+        <v>0.2415</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0601</v>
+        <v>0.2415</v>
       </c>
       <c r="N29" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1025</v>
+        <v>0.04</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0304</v>
+        <v>0.0119</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4847</v>
+        <v>-0.62</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1025</v>
+        <v>0.04</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1025</v>
+        <v>1.1159</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-1.0759</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1025</v>
+        <v>1.1159</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1025</v>
+        <v>0.5802</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-1.0759</v>
       </c>
       <c r="K30" t="n">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1025</v>
+        <v>-0.4957</v>
       </c>
       <c r="N30" t="n">
-        <v>72</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.106</v>
+        <v>-0.004</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0315</v>
+        <v>-0.0012</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.4861</v>
+        <v>-0.6398</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.106</v>
+        <v>-0.004</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.106</v>
+        <v>-0.004</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.106</v>
+        <v>-0.004</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.106</v>
+        <v>-0.004</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.106</v>
+        <v>-0.004</v>
       </c>
       <c r="N31" t="n">
         <v>89</v>
@@ -1872,78 +1872,78 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2559</v>
+        <v>-0.0546</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.076</v>
+        <v>-0.0162</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5459000000000001</v>
+        <v>-0.6627</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2559</v>
+        <v>-0.0546</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2559</v>
+        <v>-0.0546</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.2559</v>
+        <v>-0.0546</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2559</v>
+        <v>-0.0546</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2559</v>
+        <v>-0.0546</v>
       </c>
       <c r="N32" t="n">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.339</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1007</v>
+        <v>-0.029</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.579</v>
+        <v>-0.6821</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.339</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.339</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.339</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.339</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.339</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="N33" t="n">
         <v>72</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.3679</v>
+        <v>-0.1196</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1093</v>
+        <v>-0.0355</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.5905</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.3679</v>
+        <v>-0.1196</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.3032</v>
+        <v>-0.1196</v>
       </c>
       <c r="G34" t="n">
-        <v>1.9353</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-2.3032</v>
+        <v>-0.1196</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.8668</v>
+        <v>-0.1196</v>
       </c>
       <c r="J34" t="n">
-        <v>1.9353</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="L34" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.06850000000000001</v>
+        <v>-0.1196</v>
       </c>
       <c r="N34" t="n">
-        <v>264</v>
+        <v>84</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.6483</v>
+        <v>-0.3839</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1925</v>
+        <v>-0.114</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7022</v>
+        <v>-0.8113</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.6483</v>
+        <v>-0.3839</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6483</v>
+        <v>-0.3839</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6483</v>
+        <v>-0.3839</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6483</v>
+        <v>-0.3839</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6483</v>
+        <v>-0.3839</v>
       </c>
       <c r="N35" t="n">
         <v>72</v>
@@ -2056,277 +2056,277 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8389</v>
+        <v>-0.4616</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.2491</v>
+        <v>-0.1371</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7781</v>
+        <v>-0.8464</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8389</v>
+        <v>-0.4616</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.2097</v>
+        <v>-0.4616</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3708</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.2097</v>
+        <v>-0.4616</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9805</v>
+        <v>-0.4616</v>
       </c>
       <c r="J36" t="n">
-        <v>0.3708</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="L36" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6097</v>
+        <v>-0.4616</v>
       </c>
       <c r="N36" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8722</v>
+        <v>-0.6886</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.259</v>
+        <v>-0.2045</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.7914</v>
+        <v>-0.9489</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8722</v>
+        <v>-0.6886</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8722</v>
+        <v>-0.6886</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8722</v>
+        <v>-0.6886</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8722</v>
+        <v>-0.6886</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8722</v>
+        <v>-0.6886</v>
       </c>
       <c r="N37" t="n">
-        <v>134</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0865</v>
+        <v>-1.008</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3227</v>
+        <v>-0.2994</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8768</v>
+        <v>-1.0931</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0865</v>
+        <v>-1.008</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0865</v>
+        <v>-1.008</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0865</v>
+        <v>-1.008</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0865</v>
+        <v>-1.008</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0865</v>
+        <v>-1.008</v>
       </c>
       <c r="N38" t="n">
-        <v>84</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.457</v>
+        <v>-1.2367</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4327</v>
+        <v>-0.3673</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0244</v>
+        <v>-1.1963</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.457</v>
+        <v>-1.2367</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.457</v>
+        <v>-1.6209</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.3842</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.457</v>
+        <v>-1.6209</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.457</v>
+        <v>-0.8428</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.3842</v>
       </c>
       <c r="K39" t="n">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.457</v>
+        <v>-0.4586</v>
       </c>
       <c r="N39" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>PKL</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4615</v>
+        <v>-1.2759</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.434</v>
+        <v>-0.3789</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0262</v>
+        <v>-1.214</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4615</v>
+        <v>-1.2759</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1724</v>
+        <v>-1.2759</v>
       </c>
       <c r="G40" t="n">
-        <v>-1.6339</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1724</v>
+        <v>-1.2759</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1397</v>
+        <v>-1.2759</v>
       </c>
       <c r="J40" t="n">
-        <v>-1.6339</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="L40" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4942</v>
+        <v>-1.2759</v>
       </c>
       <c r="N40" t="n">
-        <v>297</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PKL</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8419</v>
+        <v>-1.4275</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.547</v>
+        <v>-0.4239</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.1777</v>
+        <v>-1.2825</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8419</v>
+        <v>-1.4275</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.8419</v>
+        <v>-2.9783</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.5508</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.8419</v>
+        <v>-2.9783</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.8419</v>
+        <v>-1.5486</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1.5508</v>
       </c>
       <c r="K41" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8419</v>
+        <v>0.00219999999999998</v>
       </c>
       <c r="N41" t="n">
-        <v>72</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6451</v>
+        <v>0.5642</v>
       </c>
       <c r="J2" t="n">
-        <v>19.353</v>
+        <v>16.926</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.26</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4286</v>
+        <v>0.3648</v>
       </c>
       <c r="J3" t="n">
-        <v>12.858</v>
+        <v>10.944</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.18</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3124</v>
+        <v>0.2656</v>
       </c>
       <c r="J4" t="n">
-        <v>9.372</v>
+        <v>7.968</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0519</v>
+        <v>0.0704</v>
       </c>
       <c r="J5" t="n">
-        <v>1.557</v>
+        <v>2.112</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.67</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.576</v>
+        <v>-0.3762</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.28</v>
+        <v>-11.286</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5223</v>
+        <v>0.474</v>
       </c>
       <c r="J7" t="n">
-        <v>15.669</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2798</v>
+        <v>0.2356</v>
       </c>
       <c r="J8" t="n">
-        <v>8.394</v>
+        <v>7.068</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0646</v>
+        <v>-0.0355</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.938</v>
+        <v>-1.065</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.83</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.338</v>
+        <v>-0.2079</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.14</v>
+        <v>-6.237</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4795</v>
+        <v>-0.3069</v>
       </c>
       <c r="J11" t="n">
-        <v>-14.385</v>
+        <v>-9.207000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2145</v>
+        <v>0.2283</v>
       </c>
       <c r="J12" t="n">
-        <v>8.58</v>
+        <v>9.132</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1785</v>
+        <v>0.1859</v>
       </c>
       <c r="J13" t="n">
-        <v>7.14</v>
+        <v>7.436</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0094</v>
+        <v>0.0011</v>
       </c>
       <c r="J14" t="n">
-        <v>0.376</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1312</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.248</v>
+        <v>-2.996</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3217</v>
+        <v>-0.1972</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.868</v>
+        <v>-7.888</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.33</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8844</v>
+        <v>0.8759</v>
       </c>
       <c r="J17" t="n">
-        <v>35.376</v>
+        <v>35.036</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.3</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8159</v>
+        <v>0.8062</v>
       </c>
       <c r="J18" t="n">
-        <v>32.636</v>
+        <v>32.248</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2592</v>
+        <v>0.3121</v>
       </c>
       <c r="J19" t="n">
-        <v>10.368</v>
+        <v>12.484</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.229</v>
+        <v>0.2838</v>
       </c>
       <c r="J20" t="n">
-        <v>9.16</v>
+        <v>11.352</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2456</v>
+        <v>-0.1712</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.824</v>
+        <v>-6.848</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.58</v>
       </c>
       <c r="I22" t="n">
-        <v>0.84</v>
+        <v>1.0342</v>
       </c>
       <c r="J22" t="n">
-        <v>30.24</v>
+        <v>37.2312</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2452</v>
+        <v>0.2764</v>
       </c>
       <c r="J23" t="n">
-        <v>8.827199999999999</v>
+        <v>9.9504</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.99</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0608</v>
+        <v>-0.0242</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1888</v>
+        <v>-0.8712</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.82</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3641</v>
+        <v>-0.2236</v>
       </c>
       <c r="J25" t="n">
-        <v>-13.1076</v>
+        <v>-8.0496</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5275</v>
+        <v>-0.3408</v>
       </c>
       <c r="J26" t="n">
-        <v>-18.99</v>
+        <v>-12.2688</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.2733</v>
+        <v>1.1694</v>
       </c>
       <c r="J27" t="n">
-        <v>45.8388</v>
+        <v>42.0984</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.32</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8937</v>
+        <v>0.8746</v>
       </c>
       <c r="J28" t="n">
-        <v>32.1732</v>
+        <v>31.4856</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1395</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>-5.022</v>
+        <v>-2.7972</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3228</v>
+        <v>-0.2564</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.6208</v>
+        <v>-9.230399999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8206</v>
+        <v>-0.7773</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.5416</v>
+        <v>-27.9828</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5689</v>
+        <v>0.5425</v>
       </c>
       <c r="J32" t="n">
-        <v>13.0847</v>
+        <v>12.4775</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.77</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3367</v>
+        <v>-0.2409</v>
       </c>
       <c r="J33" t="n">
-        <v>-7.7441</v>
+        <v>-5.5407</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.75</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3774</v>
+        <v>-0.2592</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.680199999999999</v>
+        <v>-5.9616</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.58</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.6261</v>
+        <v>-0.419</v>
       </c>
       <c r="J35" t="n">
-        <v>-14.4003</v>
+        <v>-9.637</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.48</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7533</v>
+        <v>-0.5118</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.3259</v>
+        <v>-11.7714</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>2.16</v>
       </c>
       <c r="I37" t="n">
-        <v>2.0504</v>
+        <v>1.6144</v>
       </c>
       <c r="J37" t="n">
-        <v>47.1592</v>
+        <v>37.1312</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.43</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0079</v>
+        <v>0.7528</v>
       </c>
       <c r="J38" t="n">
-        <v>23.1817</v>
+        <v>17.3144</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3651</v>
+        <v>0.4072</v>
       </c>
       <c r="J39" t="n">
-        <v>8.3973</v>
+        <v>9.365600000000001</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.09</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1541</v>
+        <v>0.2417</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5443</v>
+        <v>5.5591</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6645</v>
+        <v>-0.601</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.2835</v>
+        <v>-13.823</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2395</v>
+        <v>0.2416</v>
       </c>
       <c r="J42" t="n">
-        <v>6.4665</v>
+        <v>6.5232</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.0767</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.268</v>
+        <v>-2.0709</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1231</v>
+        <v>-0.1004</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.3237</v>
+        <v>-2.7108</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4382</v>
+        <v>-0.2831</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.8314</v>
+        <v>-7.6437</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4665</v>
+        <v>-0.3024</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.5955</v>
+        <v>-8.1648</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.42</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0457</v>
+        <v>0.7593</v>
       </c>
       <c r="J47" t="n">
-        <v>28.2339</v>
+        <v>20.5011</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.29</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.5876</v>
       </c>
       <c r="J48" t="n">
-        <v>20.3445</v>
+        <v>15.8652</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.25</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6523</v>
+        <v>0.5335</v>
       </c>
       <c r="J49" t="n">
-        <v>17.6121</v>
+        <v>14.4045</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.11</v>
       </c>
       <c r="I50" t="n">
-        <v>0.2534</v>
+        <v>0.3231</v>
       </c>
       <c r="J50" t="n">
-        <v>6.8418</v>
+        <v>8.723699999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0737</v>
+        <v>0.1464</v>
       </c>
       <c r="J51" t="n">
-        <v>1.9899</v>
+        <v>3.9528</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1388</v>
+        <v>0.1288</v>
       </c>
       <c r="J52" t="n">
-        <v>3.8864</v>
+        <v>3.6064</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1175</v>
+        <v>0.1039</v>
       </c>
       <c r="J53" t="n">
-        <v>3.29</v>
+        <v>2.9092</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1692</v>
+        <v>-0.1059</v>
       </c>
       <c r="J54" t="n">
-        <v>-4.7376</v>
+        <v>-2.9652</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.91</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1886</v>
+        <v>-0.1171</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.2808</v>
+        <v>-3.2788</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.82</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3392</v>
+        <v>-0.2122</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.4976</v>
+        <v>-5.9416</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.64</v>
       </c>
       <c r="I57" t="n">
-        <v>1.5125</v>
+        <v>1.0568</v>
       </c>
       <c r="J57" t="n">
-        <v>42.35</v>
+        <v>29.5904</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.21</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5934</v>
+        <v>0.4857</v>
       </c>
       <c r="J58" t="n">
-        <v>16.6152</v>
+        <v>13.5996</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.08</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1972</v>
+        <v>0.2544</v>
       </c>
       <c r="J59" t="n">
-        <v>5.5216</v>
+        <v>7.1232</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1076</v>
+        <v>-0.0384</v>
       </c>
       <c r="J60" t="n">
-        <v>-3.0128</v>
+        <v>-1.0752</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5448</v>
+        <v>-0.4783</v>
       </c>
       <c r="J61" t="n">
-        <v>-15.2544</v>
+        <v>-13.3924</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.63</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8318</v>
+        <v>0.5796</v>
       </c>
       <c r="J62" t="n">
-        <v>19.1314</v>
+        <v>13.3308</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.51</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6982</v>
+        <v>0.5046</v>
       </c>
       <c r="J63" t="n">
-        <v>16.0586</v>
+        <v>11.6058</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.16</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2151</v>
+        <v>0.2267</v>
       </c>
       <c r="J64" t="n">
-        <v>4.9473</v>
+        <v>5.2141</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0355</v>
+        <v>0.0697</v>
       </c>
       <c r="J65" t="n">
-        <v>0.8165</v>
+        <v>1.6031</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2338</v>
+        <v>-0.1261</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.3774</v>
+        <v>-2.9003</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.98</v>
       </c>
       <c r="I67" t="n">
-        <v>0.0423</v>
+        <v>-0.0037</v>
       </c>
       <c r="J67" t="n">
-        <v>0.9729</v>
+        <v>-0.0851</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.97</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0198</v>
+        <v>-0.0188</v>
       </c>
       <c r="J68" t="n">
-        <v>0.4554</v>
+        <v>-0.4324</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.84</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.217</v>
+        <v>-0.174</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.991</v>
+        <v>-4.002</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.72</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4334</v>
+        <v>-0.2893</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.9682</v>
+        <v>-6.6539</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.41</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.84</v>
+        <v>-0.5779</v>
       </c>
       <c r="J71" t="n">
-        <v>-19.32</v>
+        <v>-13.2917</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2178</v>
+        <v>0.2106</v>
       </c>
       <c r="J72" t="n">
-        <v>5.445</v>
+        <v>5.265</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.01</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1109</v>
+        <v>0.0788</v>
       </c>
       <c r="J73" t="n">
-        <v>2.7725</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.8</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.3335</v>
+        <v>-0.22</v>
       </c>
       <c r="J74" t="n">
-        <v>-8.3375</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.74</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4267</v>
+        <v>-0.2784</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.6675</v>
+        <v>-6.96</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.61</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6052</v>
+        <v>-0.4015</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.13</v>
+        <v>-10.0375</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.56</v>
       </c>
       <c r="I77" t="n">
-        <v>1.3483</v>
+        <v>0.9484</v>
       </c>
       <c r="J77" t="n">
-        <v>33.7075</v>
+        <v>23.71</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.23</v>
       </c>
       <c r="I78" t="n">
-        <v>0.6292</v>
+        <v>0.5107</v>
       </c>
       <c r="J78" t="n">
-        <v>15.73</v>
+        <v>12.7675</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2736</v>
+        <v>0.3307</v>
       </c>
       <c r="J79" t="n">
-        <v>6.84</v>
+        <v>8.2675</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0214</v>
+        <v>0.0885</v>
       </c>
       <c r="J80" t="n">
-        <v>0.535</v>
+        <v>2.2125</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.99</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.1759</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="J81" t="n">
-        <v>-4.3975</v>
+        <v>-2.4875</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.8</v>
       </c>
       <c r="I82" t="n">
-        <v>1.708</v>
+        <v>1.4673</v>
       </c>
       <c r="J82" t="n">
-        <v>40.992</v>
+        <v>35.2152</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.78</v>
       </c>
       <c r="I83" t="n">
-        <v>1.6726</v>
+        <v>1.444</v>
       </c>
       <c r="J83" t="n">
-        <v>40.1424</v>
+        <v>34.656</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.52</v>
       </c>
       <c r="I84" t="n">
-        <v>1.1832</v>
+        <v>1.1336</v>
       </c>
       <c r="J84" t="n">
-        <v>28.3968</v>
+        <v>27.2064</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.5253</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.2872</v>
+        <v>-12.6072</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6452</v>
+        <v>-0.5796</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.4848</v>
+        <v>-13.9104</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.87</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1224</v>
+        <v>-0.1216</v>
       </c>
       <c r="J87" t="n">
-        <v>-2.9376</v>
+        <v>-2.9184</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.82</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2041</v>
+        <v>-0.1775</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.8984</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.76</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.3005</v>
+        <v>-0.2398</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.212</v>
+        <v>-5.7552</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.63</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.5296</v>
+        <v>-0.3603</v>
       </c>
       <c r="J90" t="n">
-        <v>-12.7104</v>
+        <v>-8.6472</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.8487</v>
+        <v>-0.5846</v>
       </c>
       <c r="J91" t="n">
-        <v>-20.3688</v>
+        <v>-14.0304</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.51</v>
       </c>
       <c r="I92" t="n">
-        <v>1.2481</v>
+        <v>1.1573</v>
       </c>
       <c r="J92" t="n">
-        <v>33.6987</v>
+        <v>31.2471</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6263</v>
+        <v>0.633</v>
       </c>
       <c r="J93" t="n">
-        <v>16.9101</v>
+        <v>17.091</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.15</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3858</v>
+        <v>0.4395</v>
       </c>
       <c r="J94" t="n">
-        <v>10.4166</v>
+        <v>11.8665</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.055</v>
+        <v>0.1222</v>
       </c>
       <c r="J95" t="n">
-        <v>1.485</v>
+        <v>3.2994</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.01</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.0602</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>-1.6254</v>
+        <v>0.2511</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.29</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5251</v>
+        <v>0.621</v>
       </c>
       <c r="J97" t="n">
-        <v>14.1777</v>
+        <v>16.767</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2477</v>
+        <v>0.2609</v>
       </c>
       <c r="J98" t="n">
-        <v>6.6879</v>
+        <v>7.0443</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1713</v>
+        <v>-0.1063</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.6251</v>
+        <v>-2.8701</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.87</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2609</v>
+        <v>-0.1609</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.0443</v>
+        <v>-4.3443</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6866</v>
+        <v>-0.4602</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.5382</v>
+        <v>-12.4254</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.11</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3386</v>
+        <v>0.3661</v>
       </c>
       <c r="J102" t="n">
-        <v>7.7878</v>
+        <v>8.420299999999999</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0116</v>
+        <v>-0.0413</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.2668</v>
+        <v>-0.9499</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.88</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1382</v>
+        <v>-0.1266</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.1786</v>
+        <v>-2.9118</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.47</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7641</v>
+        <v>-0.5199</v>
       </c>
       <c r="J105" t="n">
-        <v>-17.5743</v>
+        <v>-11.9577</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.4</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8484</v>
+        <v>-0.5844</v>
       </c>
       <c r="J106" t="n">
-        <v>-19.5132</v>
+        <v>-13.4412</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.71</v>
       </c>
       <c r="I107" t="n">
-        <v>1.5261</v>
+        <v>1.3518</v>
       </c>
       <c r="J107" t="n">
-        <v>35.1003</v>
+        <v>31.0914</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.67</v>
       </c>
       <c r="I108" t="n">
-        <v>1.4522</v>
+        <v>1.3049</v>
       </c>
       <c r="J108" t="n">
-        <v>33.4006</v>
+        <v>30.0127</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.5</v>
       </c>
       <c r="I109" t="n">
-        <v>1.1179</v>
+        <v>1.1025</v>
       </c>
       <c r="J109" t="n">
-        <v>25.7117</v>
+        <v>25.3575</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.23</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4834</v>
+        <v>0.5906</v>
       </c>
       <c r="J110" t="n">
-        <v>11.1182</v>
+        <v>13.5838</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3841</v>
+        <v>-0.2986</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.834300000000001</v>
+        <v>-6.8678</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.635</v>
+        <v>0.7728</v>
       </c>
       <c r="J112" t="n">
-        <v>17.78</v>
+        <v>21.6384</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.176</v>
+        <v>0.1845</v>
       </c>
       <c r="J113" t="n">
-        <v>4.928</v>
+        <v>5.166</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.043</v>
+        <v>0.0383</v>
       </c>
       <c r="J114" t="n">
-        <v>1.204</v>
+        <v>1.0724</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3385</v>
+        <v>-0.2082</v>
       </c>
       <c r="J115" t="n">
-        <v>-9.478</v>
+        <v>-5.8296</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5454</v>
+        <v>-0.3547</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.2712</v>
+        <v>-9.9316</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9268</v>
+        <v>0.9197</v>
       </c>
       <c r="J117" t="n">
-        <v>25.9504</v>
+        <v>25.7516</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6942</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J118" t="n">
-        <v>19.4376</v>
+        <v>19.236</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5651</v>
+        <v>0.5666</v>
       </c>
       <c r="J119" t="n">
-        <v>15.8228</v>
+        <v>15.8648</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.03</v>
       </c>
       <c r="I120" t="n">
-        <v>0.031</v>
+        <v>0.094</v>
       </c>
       <c r="J120" t="n">
-        <v>0.868</v>
+        <v>2.632</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.98</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2095</v>
+        <v>-0.135</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.866</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.23</v>
       </c>
       <c r="I122" t="n">
-        <v>0.739</v>
+        <v>0.6965</v>
       </c>
       <c r="J122" t="n">
-        <v>22.17</v>
+        <v>20.895</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.22</v>
       </c>
       <c r="I123" t="n">
-        <v>0.7146</v>
+        <v>0.671</v>
       </c>
       <c r="J123" t="n">
-        <v>21.438</v>
+        <v>20.13</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.95</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2384</v>
+        <v>-0.1983</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.152</v>
+        <v>-5.949</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5125</v>
+        <v>-0.4624</v>
       </c>
       <c r="J125" t="n">
-        <v>-15.375</v>
+        <v>-13.872</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.76</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7669</v>
+        <v>-0.7251</v>
       </c>
       <c r="J126" t="n">
-        <v>-23.007</v>
+        <v>-21.753</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4243</v>
+        <v>0.4965</v>
       </c>
       <c r="J127" t="n">
-        <v>12.729</v>
+        <v>14.895</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2267</v>
+        <v>0.256</v>
       </c>
       <c r="J128" t="n">
-        <v>6.801</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1103</v>
+        <v>0.1319</v>
       </c>
       <c r="J129" t="n">
-        <v>3.309</v>
+        <v>3.957</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.99</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0624</v>
+        <v>-0.0245</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.872</v>
+        <v>-0.735</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.84</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3355</v>
+        <v>-0.2036</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.065</v>
+        <v>-6.108</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.29</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7994</v>
+        <v>0.7867</v>
       </c>
       <c r="J132" t="n">
-        <v>20.7844</v>
+        <v>20.4542</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.24</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6792</v>
+        <v>0.6676</v>
       </c>
       <c r="J133" t="n">
-        <v>17.6592</v>
+        <v>17.3576</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.21</v>
       </c>
       <c r="I134" t="n">
-        <v>0.6029</v>
+        <v>0.5948</v>
       </c>
       <c r="J134" t="n">
-        <v>15.6754</v>
+        <v>15.4648</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1416</v>
+        <v>0.1973</v>
       </c>
       <c r="J135" t="n">
-        <v>3.6816</v>
+        <v>5.1298</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.372</v>
+        <v>-0.3</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.672000000000001</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.16</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3468</v>
+        <v>0.3845</v>
       </c>
       <c r="J137" t="n">
-        <v>9.0168</v>
+        <v>9.997</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.13</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3004</v>
+        <v>0.3253</v>
       </c>
       <c r="J138" t="n">
-        <v>7.8104</v>
+        <v>8.457800000000001</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.87</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.2572</v>
+        <v>-0.1598</v>
       </c>
       <c r="J139" t="n">
-        <v>-6.6872</v>
+        <v>-4.1548</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3374</v>
+        <v>-0.2115</v>
       </c>
       <c r="J140" t="n">
-        <v>-8.772399999999999</v>
+        <v>-5.499</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4946</v>
+        <v>-0.3194</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.8596</v>
+        <v>-8.304399999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.19</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4074</v>
+        <v>0.4604</v>
       </c>
       <c r="J142" t="n">
-        <v>10.185</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.1154</v>
+        <v>0.0915</v>
       </c>
       <c r="J143" t="n">
-        <v>2.885</v>
+        <v>2.2875</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2728</v>
+        <v>-0.1757</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.82</v>
+        <v>-4.3925</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3537</v>
+        <v>-0.2261</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.842499999999999</v>
+        <v>-5.6525</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6157</v>
+        <v>-0.408</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.3925</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>1.431</v>
+        <v>1.2763</v>
       </c>
       <c r="J147" t="n">
-        <v>35.775</v>
+        <v>31.9075</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6629</v>
+        <v>0.6606</v>
       </c>
       <c r="J148" t="n">
-        <v>16.5725</v>
+        <v>16.515</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.13</v>
       </c>
       <c r="I149" t="n">
-        <v>0.339</v>
+        <v>0.3907</v>
       </c>
       <c r="J149" t="n">
-        <v>8.475</v>
+        <v>9.7675</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.07</v>
       </c>
       <c r="I150" t="n">
-        <v>0.16</v>
+        <v>0.2217</v>
       </c>
       <c r="J150" t="n">
-        <v>4</v>
+        <v>5.5425</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.82</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6747</v>
+        <v>-0.6162</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.8675</v>
+        <v>-15.405</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0751</v>
+        <v>0.0323</v>
       </c>
       <c r="J152" t="n">
-        <v>1.4269</v>
+        <v>0.6137</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0327</v>
+        <v>-0.0554</v>
       </c>
       <c r="J153" t="n">
-        <v>-0.6213</v>
+        <v>-1.0526</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.79</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2929</v>
+        <v>-0.2217</v>
       </c>
       <c r="J154" t="n">
-        <v>-5.5651</v>
+        <v>-4.2123</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.64</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.5435</v>
+        <v>-0.3622</v>
       </c>
       <c r="J155" t="n">
-        <v>-10.3265</v>
+        <v>-6.8818</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.47</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7648</v>
+        <v>-0.5205</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.5312</v>
+        <v>-9.8895</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.57</v>
       </c>
       <c r="I157" t="n">
-        <v>1.2669</v>
+        <v>1.1886</v>
       </c>
       <c r="J157" t="n">
-        <v>24.0711</v>
+        <v>22.5834</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.43</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9722</v>
+        <v>1.0147</v>
       </c>
       <c r="J158" t="n">
-        <v>18.4718</v>
+        <v>19.2793</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.37</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.9091</v>
       </c>
       <c r="J159" t="n">
-        <v>15.466</v>
+        <v>17.2729</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.34</v>
       </c>
       <c r="I160" t="n">
-        <v>0.7432</v>
+        <v>0.8451</v>
       </c>
       <c r="J160" t="n">
-        <v>14.1208</v>
+        <v>16.0569</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.28</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6048</v>
+        <v>0.7109</v>
       </c>
       <c r="J161" t="n">
-        <v>11.4912</v>
+        <v>13.5071</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.78</v>
       </c>
       <c r="I162" t="n">
-        <v>1.7245</v>
+        <v>1.4752</v>
       </c>
       <c r="J162" t="n">
-        <v>50.0105</v>
+        <v>42.7808</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7625</v>
+        <v>0.7817</v>
       </c>
       <c r="J163" t="n">
-        <v>22.1125</v>
+        <v>22.6693</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5105</v>
+        <v>0.5764</v>
       </c>
       <c r="J164" t="n">
-        <v>14.8045</v>
+        <v>16.7156</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.15</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3516</v>
+        <v>0.4267</v>
       </c>
       <c r="J165" t="n">
-        <v>10.1964</v>
+        <v>12.3743</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.8</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.741</v>
+        <v>-0.6862</v>
       </c>
       <c r="J166" t="n">
-        <v>-21.489</v>
+        <v>-19.8998</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.99</v>
       </c>
       <c r="I167" t="n">
-        <v>0.0493</v>
+        <v>0.006</v>
       </c>
       <c r="J167" t="n">
-        <v>1.4297</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.86</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.205</v>
+        <v>-0.1591</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.945</v>
+        <v>-4.6139</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2232</v>
+        <v>-0.1694</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.4728</v>
+        <v>-4.9126</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.76</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3896</v>
+        <v>-0.2567</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.2984</v>
+        <v>-7.4443</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5206</v>
+        <v>-0.3427</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.0974</v>
+        <v>-9.9383</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>2.07</v>
       </c>
       <c r="I172" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J172" t="n">
-        <v>57.6604</v>
+        <v>51.3464</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2671</v>
+        <v>0.3313</v>
       </c>
       <c r="J173" t="n">
-        <v>7.4788</v>
+        <v>9.276400000000001</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1174</v>
+        <v>0.1851</v>
       </c>
       <c r="J174" t="n">
-        <v>3.2872</v>
+        <v>5.1828</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.98</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2222</v>
+        <v>-0.1437</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.2216</v>
+        <v>-4.0236</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8217</v>
+        <v>-0.7759</v>
       </c>
       <c r="J176" t="n">
-        <v>-23.0076</v>
+        <v>-21.7252</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.2</v>
       </c>
       <c r="I177" t="n">
-        <v>0.421</v>
+        <v>0.4786</v>
       </c>
       <c r="J177" t="n">
-        <v>11.788</v>
+        <v>13.4008</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.97</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0288</v>
+        <v>-0.04</v>
       </c>
       <c r="J178" t="n">
-        <v>-0.8064</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.86</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2564</v>
+        <v>-0.1656</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.1792</v>
+        <v>-4.6368</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.83</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.307</v>
+        <v>-0.1963</v>
       </c>
       <c r="J180" t="n">
-        <v>-8.596</v>
+        <v>-5.4964</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.62</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6034</v>
+        <v>-0.399</v>
       </c>
       <c r="J181" t="n">
-        <v>-16.8952</v>
+        <v>-11.172</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2652</v>
+        <v>0.2765</v>
       </c>
       <c r="J182" t="n">
-        <v>7.1604</v>
+        <v>7.4655</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.92</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1355</v>
+        <v>-0.1028</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.6585</v>
+        <v>-2.7756</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.182</v>
+        <v>-0.1244</v>
       </c>
       <c r="J184" t="n">
-        <v>-4.914</v>
+        <v>-3.3588</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.84</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.293</v>
+        <v>-0.1868</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.911</v>
+        <v>-5.0436</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.75</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4302</v>
+        <v>-0.2763</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.6154</v>
+        <v>-7.4601</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.49</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1785</v>
+        <v>1.1178</v>
       </c>
       <c r="J187" t="n">
-        <v>31.8195</v>
+        <v>30.1806</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.34</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8571</v>
+        <v>0.8714</v>
       </c>
       <c r="J188" t="n">
-        <v>23.1417</v>
+        <v>23.5278</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.5647</v>
+        <v>0.6236</v>
       </c>
       <c r="J189" t="n">
-        <v>15.2469</v>
+        <v>16.8372</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.4839</v>
+        <v>0.5523</v>
       </c>
       <c r="J190" t="n">
-        <v>13.0653</v>
+        <v>14.9121</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.98</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2395</v>
+        <v>-0.1566</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.4665</v>
+        <v>-4.2282</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.15</v>
       </c>
       <c r="I192" t="n">
-        <v>2.0593</v>
+        <v>1.814</v>
       </c>
       <c r="J192" t="n">
-        <v>37.0674</v>
+        <v>32.652</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.54</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1027</v>
+        <v>1.1361</v>
       </c>
       <c r="J193" t="n">
-        <v>19.8486</v>
+        <v>20.4498</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.51</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0365</v>
+        <v>1.1014</v>
       </c>
       <c r="J194" t="n">
-        <v>18.657</v>
+        <v>19.8252</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.38</v>
       </c>
       <c r="I195" t="n">
-        <v>0.7641</v>
+        <v>0.9019</v>
       </c>
       <c r="J195" t="n">
-        <v>13.7538</v>
+        <v>16.2342</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.21</v>
       </c>
       <c r="I196" t="n">
-        <v>0.3945</v>
+        <v>0.5124</v>
       </c>
       <c r="J196" t="n">
-        <v>7.101</v>
+        <v>9.2232</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.02</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2587</v>
+        <v>0.2801</v>
       </c>
       <c r="J197" t="n">
-        <v>4.6566</v>
+        <v>5.0418</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.82</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1478</v>
+        <v>-0.1437</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.6604</v>
+        <v>-2.5866</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.55</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.5967</v>
+        <v>-0.4162</v>
       </c>
       <c r="J199" t="n">
-        <v>-10.7406</v>
+        <v>-7.4916</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.41</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.5481</v>
       </c>
       <c r="J200" t="n">
-        <v>-14.3622</v>
+        <v>-9.8658</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.14</v>
       </c>
       <c r="I201" t="n">
-        <v>-1.1289</v>
+        <v>-0.8098</v>
       </c>
       <c r="J201" t="n">
-        <v>-20.3202</v>
+        <v>-14.5764</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.85</v>
       </c>
       <c r="I202" t="n">
-        <v>1.7242</v>
+        <v>1.4885</v>
       </c>
       <c r="J202" t="n">
-        <v>34.484</v>
+        <v>29.77</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.5</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0259</v>
+        <v>1.0914</v>
       </c>
       <c r="J203" t="n">
-        <v>20.518</v>
+        <v>21.828</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.47</v>
       </c>
       <c r="I204" t="n">
-        <v>0.9611</v>
+        <v>1.0555</v>
       </c>
       <c r="J204" t="n">
-        <v>19.222</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.46</v>
       </c>
       <c r="I205" t="n">
-        <v>0.9398</v>
+        <v>1.0428</v>
       </c>
       <c r="J205" t="n">
-        <v>18.796</v>
+        <v>20.856</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.41</v>
       </c>
       <c r="I206" t="n">
-        <v>0.8343</v>
+        <v>0.965</v>
       </c>
       <c r="J206" t="n">
-        <v>16.686</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.92</v>
       </c>
       <c r="I207" t="n">
-        <v>0.0071</v>
+        <v>-0.0295</v>
       </c>
       <c r="J207" t="n">
-        <v>0.142</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.76</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2541</v>
+        <v>-0.2188</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.082</v>
+        <v>-4.376</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.67</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3945</v>
+        <v>-0.3111</v>
       </c>
       <c r="J209" t="n">
-        <v>-7.89</v>
+        <v>-6.222</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.42</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.7912</v>
+        <v>-0.5427</v>
       </c>
       <c r="J210" t="n">
-        <v>-15.824</v>
+        <v>-10.854</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.28</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.9669</v>
+        <v>-0.6768</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.338</v>
+        <v>-13.536</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.73</v>
       </c>
       <c r="I212" t="n">
-        <v>1.6417</v>
+        <v>1.4189</v>
       </c>
       <c r="J212" t="n">
-        <v>45.9676</v>
+        <v>39.7292</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.53</v>
       </c>
       <c r="I213" t="n">
-        <v>1.2652</v>
+        <v>1.1714</v>
       </c>
       <c r="J213" t="n">
-        <v>35.4256</v>
+        <v>32.7992</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.08</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1624</v>
+        <v>0.2367</v>
       </c>
       <c r="J214" t="n">
-        <v>4.5472</v>
+        <v>6.6276</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.99</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.1935</v>
+        <v>-0.112</v>
       </c>
       <c r="J215" t="n">
-        <v>-5.418</v>
+        <v>-3.136</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6415</v>
+        <v>-0.5782</v>
       </c>
       <c r="J216" t="n">
-        <v>-17.962</v>
+        <v>-16.1896</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.23</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4677</v>
+        <v>0.5412</v>
       </c>
       <c r="J217" t="n">
-        <v>13.0956</v>
+        <v>15.1536</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.15</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3517</v>
+        <v>0.3863</v>
       </c>
       <c r="J218" t="n">
-        <v>9.8476</v>
+        <v>10.8164</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1852</v>
+        <v>-0.1337</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.1856</v>
+        <v>-3.7436</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.73</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4535</v>
+        <v>-0.2933</v>
       </c>
       <c r="J220" t="n">
-        <v>-12.698</v>
+        <v>-8.212400000000001</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.42</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.8419</v>
+        <v>-0.5797</v>
       </c>
       <c r="J221" t="n">
-        <v>-23.5732</v>
+        <v>-16.2316</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3313/event_3313_evp_summary.xlsx
+++ b/database/event/3313/event_3313_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0324</v>
+        <v>6.1551</v>
       </c>
       <c r="C2" t="n">
-        <v>1.7915</v>
+        <v>1.828</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0853</v>
+        <v>2.1777</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0324</v>
+        <v>6.1551</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5004</v>
+        <v>2.4501</v>
       </c>
       <c r="G2" t="n">
-        <v>3.532</v>
+        <v>3.705</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3236</v>
+        <v>3.1895</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7281</v>
+        <v>1.7223</v>
       </c>
       <c r="J2" t="n">
-        <v>3.532</v>
+        <v>3.705</v>
       </c>
       <c r="K2" t="n">
         <v>108</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>5.2601</v>
+        <v>5.4273</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.24</v>
+        <v>5.2905</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5562</v>
+        <v>1.5712</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7276</v>
+        <v>1.7841</v>
       </c>
       <c r="E3" t="n">
-        <v>5.24</v>
+        <v>5.2905</v>
       </c>
       <c r="F3" t="n">
-        <v>2.359</v>
+        <v>2.2737</v>
       </c>
       <c r="G3" t="n">
-        <v>2.881</v>
+        <v>3.0168</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8252</v>
+        <v>2.6076</v>
       </c>
       <c r="I3" t="n">
-        <v>1.469</v>
+        <v>1.4081</v>
       </c>
       <c r="J3" t="n">
-        <v>2.881</v>
+        <v>3.0168</v>
       </c>
       <c r="K3" t="n">
         <v>115</v>
@@ -575,7 +575,7 @@
         <v>182</v>
       </c>
       <c r="M3" t="n">
-        <v>4.35</v>
+        <v>4.4249</v>
       </c>
       <c r="N3" t="n">
         <v>297</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3879</v>
+        <v>4.4926</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3031</v>
+        <v>1.3342</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3429</v>
+        <v>1.4209</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3879</v>
+        <v>4.4926</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7391</v>
+        <v>3.7588</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6488</v>
+        <v>0.7338</v>
       </c>
       <c r="H4" t="n">
-        <v>7.688</v>
+        <v>7.5075</v>
       </c>
       <c r="I4" t="n">
-        <v>3.9974</v>
+        <v>4.054</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6488</v>
+        <v>0.7338</v>
       </c>
       <c r="K4" t="n">
         <v>108</v>
@@ -621,7 +621,7 @@
         <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6462</v>
+        <v>4.787800000000001</v>
       </c>
       <c r="N4" t="n">
         <v>264</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2217</v>
+        <v>4.1755</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2538</v>
+        <v>1.2401</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2679</v>
+        <v>1.2766</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2217</v>
+        <v>4.1755</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1639</v>
+        <v>3.0858</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0578</v>
+        <v>1.0897</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6613</v>
+        <v>5.2869</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9436</v>
+        <v>2.8549</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0578</v>
+        <v>1.0897</v>
       </c>
       <c r="K5" t="n">
         <v>115</v>
@@ -667,7 +667,7 @@
         <v>182</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0014</v>
+        <v>3.9446</v>
       </c>
       <c r="N5" t="n">
         <v>297</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9236</v>
+        <v>3.8585</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1653</v>
+        <v>1.1459</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1333</v>
+        <v>1.1323</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9236</v>
+        <v>3.8585</v>
       </c>
       <c r="F6" t="n">
-        <v>3.166</v>
+        <v>3.0545</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.804</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6688</v>
+        <v>5.1838</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9475</v>
+        <v>2.7992</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.804</v>
       </c>
       <c r="K6" t="n">
         <v>115</v>
@@ -713,7 +713,7 @@
         <v>182</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7051</v>
+        <v>3.6032</v>
       </c>
       <c r="N6" t="n">
         <v>297</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>olofmeister</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3526</v>
+        <v>3.3173</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9957</v>
+        <v>0.9852</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8859</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3526</v>
+        <v>3.3173</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2306</v>
+        <v>2.3679</v>
       </c>
       <c r="G7" t="n">
-        <v>0.122</v>
+        <v>0.9494</v>
       </c>
       <c r="H7" t="n">
-        <v>5.8963</v>
+        <v>2.9184</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0658</v>
+        <v>1.5759</v>
       </c>
       <c r="J7" t="n">
-        <v>0.122</v>
+        <v>0.9494</v>
       </c>
       <c r="K7" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="L7" t="n">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1878</v>
+        <v>2.5253</v>
       </c>
       <c r="N7" t="n">
-        <v>297</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>olofmeister</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3348</v>
+        <v>3.2986</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9903999999999999</v>
+        <v>0.9796</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8675</v>
+        <v>0.8774</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3348</v>
+        <v>3.2986</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4381</v>
+        <v>3.1327</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.1659</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1039</v>
+        <v>5.4418</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6139</v>
+        <v>2.9385</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.1659</v>
       </c>
       <c r="K8" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L8" t="n">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5106</v>
+        <v>3.1044</v>
       </c>
       <c r="N8" t="n">
-        <v>264</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8402</v>
+        <v>2.8273</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8435</v>
+        <v>0.8397</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6442</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8402</v>
+        <v>2.8273</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6615</v>
+        <v>2.6063</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1787</v>
+        <v>0.221</v>
       </c>
       <c r="H9" t="n">
-        <v>3.891</v>
+        <v>3.7049</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0231</v>
+        <v>2.0006</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1787</v>
+        <v>0.221</v>
       </c>
       <c r="K9" t="n">
         <v>56</v>
@@ -851,7 +851,7 @@
         <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2018</v>
+        <v>2.2216</v>
       </c>
       <c r="N9" t="n">
         <v>132</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6703</v>
+        <v>2.5935</v>
       </c>
       <c r="C10" t="n">
-        <v>0.793</v>
+        <v>0.7702</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5675</v>
+        <v>0.5564</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6703</v>
+        <v>2.5935</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4819</v>
+        <v>2.4052</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1884</v>
+        <v>0.1883</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2584</v>
+        <v>3.0415</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6942</v>
+        <v>1.6424</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1884</v>
+        <v>0.1883</v>
       </c>
       <c r="K10" t="n">
         <v>56</v>
@@ -897,7 +897,7 @@
         <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8826</v>
+        <v>1.8307</v>
       </c>
       <c r="N10" t="n">
         <v>132</v>
@@ -906,127 +906,127 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3529</v>
+        <v>2.2933</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6988</v>
+        <v>0.6811</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4242</v>
+        <v>0.4198</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3529</v>
+        <v>2.2933</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6888</v>
+        <v>1.908</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3359</v>
+        <v>0.3853</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9875</v>
+        <v>1.908</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0733</v>
+        <v>1.0303</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3359</v>
+        <v>0.3853</v>
       </c>
       <c r="K11" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L11" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7374</v>
+        <v>1.4156</v>
       </c>
       <c r="N11" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3269</v>
+        <v>2.2748</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6911</v>
+        <v>0.6756</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4125</v>
+        <v>0.4113</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3269</v>
+        <v>2.2748</v>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2.6501</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3069</v>
+        <v>-0.3753</v>
       </c>
       <c r="H12" t="n">
-        <v>2.02</v>
+        <v>3.8495</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0503</v>
+        <v>2.0787</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3069</v>
+        <v>-0.3753</v>
       </c>
       <c r="K12" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L12" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>1.3572</v>
+        <v>1.7034</v>
       </c>
       <c r="N12" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2677</v>
+        <v>2.2369</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6735</v>
+        <v>0.6643</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3857</v>
+        <v>0.3941</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2677</v>
+        <v>2.2369</v>
       </c>
       <c r="F13" t="n">
-        <v>2.609</v>
+        <v>2.6055</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3413</v>
+        <v>-0.3686</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7062</v>
+        <v>3.7023</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9271</v>
+        <v>1.9992</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3413</v>
+        <v>-0.3686</v>
       </c>
       <c r="K13" t="n">
         <v>46</v>
@@ -1035,7 +1035,7 @@
         <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5858</v>
+        <v>1.6306</v>
       </c>
       <c r="N13" t="n">
         <v>96</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.143</v>
+        <v>2.0713</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6364</v>
+        <v>0.6151</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3294</v>
+        <v>0.3187</v>
       </c>
       <c r="E14" t="n">
-        <v>2.143</v>
+        <v>2.0713</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9029</v>
+        <v>1.8008</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2401</v>
+        <v>0.2705</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9029</v>
+        <v>1.8008</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9724</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2401</v>
+        <v>0.2705</v>
       </c>
       <c r="K14" t="n">
         <v>46</v>
@@ -1081,7 +1081,7 @@
         <v>50</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2295</v>
+        <v>1.2429</v>
       </c>
       <c r="N14" t="n">
         <v>96</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9088</v>
+        <v>1.8289</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5669</v>
+        <v>0.5432</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2237</v>
+        <v>0.2083</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9088</v>
+        <v>1.8289</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6109</v>
+        <v>2.5599</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.731</v>
       </c>
       <c r="H15" t="n">
-        <v>3.713</v>
+        <v>3.5517</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9306</v>
+        <v>1.9179</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.731</v>
       </c>
       <c r="K15" t="n">
         <v>46</v>
@@ -1127,7 +1127,7 @@
         <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>1.2285</v>
+        <v>1.1869</v>
       </c>
       <c r="N15" t="n">
         <v>96</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8428</v>
+        <v>1.7096</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5473</v>
+        <v>0.5077</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1939</v>
+        <v>0.154</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8428</v>
+        <v>1.7096</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4595</v>
+        <v>2.3637</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6167</v>
+        <v>-0.6541</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1793</v>
+        <v>2.9045</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6531</v>
+        <v>1.5684</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6167</v>
+        <v>-0.6541</v>
       </c>
       <c r="K16" t="n">
         <v>56</v>
@@ -1173,7 +1173,7 @@
         <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0364</v>
+        <v>0.9143</v>
       </c>
       <c r="N16" t="n">
         <v>132</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5528</v>
+        <v>1.4237</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4612</v>
+        <v>0.4228</v>
       </c>
       <c r="D17" t="n">
-        <v>0.063</v>
+        <v>0.0239</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5528</v>
+        <v>1.4237</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5528</v>
+        <v>1.4237</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5528</v>
+        <v>1.4237</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5528</v>
+        <v>1.4237</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.5528</v>
+        <v>1.4237</v>
       </c>
       <c r="N17" t="n">
         <v>89</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0021</v>
+        <v>1.0926</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2976</v>
+        <v>0.3245</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1856</v>
+        <v>-0.1268</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0021</v>
+        <v>1.0926</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2194</v>
+        <v>-0.1372</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2215</v>
+        <v>1.2298</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2194</v>
+        <v>-0.1372</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1141</v>
+        <v>-0.0741</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2215</v>
+        <v>1.2298</v>
       </c>
       <c r="K18" t="n">
         <v>108</v>
@@ -1265,7 +1265,7 @@
         <v>156</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1074</v>
+        <v>1.1557</v>
       </c>
       <c r="N18" t="n">
         <v>264</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0002</v>
+        <v>0.9142</v>
       </c>
       <c r="C19" t="n">
-        <v>0.297</v>
+        <v>0.2715</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1865</v>
+        <v>-0.208</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0002</v>
+        <v>0.9142</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0002</v>
+        <v>0.9142</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0002</v>
+        <v>0.9142</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0002</v>
+        <v>0.9142</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0002</v>
+        <v>0.9142</v>
       </c>
       <c r="N19" t="n">
         <v>89</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8028</v>
+        <v>0.7796</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2384</v>
+        <v>0.2315</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2756</v>
+        <v>-0.2693</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8028</v>
+        <v>0.7796</v>
       </c>
       <c r="F20" t="n">
-        <v>1.073</v>
+        <v>1.0602</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2702</v>
+        <v>-0.2806</v>
       </c>
       <c r="H20" t="n">
-        <v>1.073</v>
+        <v>1.0602</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5579</v>
+        <v>0.5725</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2702</v>
+        <v>-0.2806</v>
       </c>
       <c r="K20" t="n">
         <v>46</v>
@@ -1357,7 +1357,7 @@
         <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2877</v>
+        <v>0.2919</v>
       </c>
       <c r="N20" t="n">
         <v>96</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7463</v>
+        <v>0.6448</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2216</v>
+        <v>0.1915</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3011</v>
+        <v>-0.3307</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7463</v>
+        <v>0.6448</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7463</v>
+        <v>0.6448</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7463</v>
+        <v>0.6448</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7463</v>
+        <v>0.6448</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7463</v>
+        <v>0.6448</v>
       </c>
       <c r="N21" t="n">
         <v>134</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6008</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1858</v>
+        <v>0.1784</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3556</v>
+        <v>-0.3507</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6008</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6008</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6008</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6008</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6254999999999999</v>
+        <v>0.6008</v>
       </c>
       <c r="N22" t="n">
         <v>84</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5869</v>
+        <v>0.5225</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1743</v>
+        <v>0.1552</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3731</v>
+        <v>-0.3864</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5869</v>
+        <v>0.5225</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5869</v>
+        <v>0.5225</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5869</v>
+        <v>0.5225</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5869</v>
+        <v>0.5225</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5869</v>
+        <v>0.5225</v>
       </c>
       <c r="N23" t="n">
         <v>89</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5028</v>
+        <v>0.4697</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1493</v>
+        <v>0.1395</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.411</v>
+        <v>-0.4104</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5028</v>
+        <v>0.4697</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5028</v>
+        <v>0.4697</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5028</v>
+        <v>0.4697</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5028</v>
+        <v>0.4697</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5028</v>
+        <v>0.4697</v>
       </c>
       <c r="N24" t="n">
         <v>134</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4055</v>
+        <v>0.33</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1204</v>
+        <v>0.098</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.455</v>
+        <v>-0.474</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4055</v>
+        <v>0.33</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4055</v>
+        <v>0.33</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4055</v>
+        <v>0.33</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4055</v>
+        <v>0.33</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4055</v>
+        <v>0.33</v>
       </c>
       <c r="N25" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3909</v>
+        <v>0.3253</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1161</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4615</v>
+        <v>-0.4761</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3909</v>
+        <v>0.3253</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3909</v>
+        <v>0.3253</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3909</v>
+        <v>0.3253</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3909</v>
+        <v>0.3253</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3909</v>
+        <v>0.3253</v>
       </c>
       <c r="N26" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3474</v>
+        <v>0.2846</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1032</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4812</v>
+        <v>-0.4946</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3474</v>
+        <v>0.2846</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3474</v>
+        <v>0.2846</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.3474</v>
+        <v>0.2846</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3474</v>
+        <v>0.2846</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3474</v>
+        <v>0.2846</v>
       </c>
       <c r="N27" t="n">
         <v>72</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2943</v>
+        <v>0.2601</v>
       </c>
       <c r="C28" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.0772</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5052</v>
+        <v>-0.5058</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2943</v>
+        <v>0.2601</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2943</v>
+        <v>0.2601</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2943</v>
+        <v>0.2601</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2943</v>
+        <v>0.2601</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2943</v>
+        <v>0.2601</v>
       </c>
       <c r="N28" t="n">
         <v>84</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.2415</v>
+        <v>0.233</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0717</v>
+        <v>0.0692</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.529</v>
+        <v>-0.5181</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2415</v>
+        <v>0.233</v>
       </c>
       <c r="F29" t="n">
-        <v>0.2415</v>
+        <v>0.233</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.2415</v>
+        <v>0.233</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2415</v>
+        <v>0.233</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2415</v>
+        <v>0.233</v>
       </c>
       <c r="N29" t="n">
         <v>84</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.04</v>
+        <v>0.0639</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0119</v>
+        <v>0.019</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.62</v>
+        <v>-0.5951</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04</v>
+        <v>0.0639</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1159</v>
+        <v>1.1208</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.0759</v>
+        <v>-1.0569</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1159</v>
+        <v>1.1208</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5802</v>
+        <v>0.6052</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.0759</v>
+        <v>-1.0569</v>
       </c>
       <c r="K30" t="n">
         <v>115</v>
@@ -1817,7 +1817,7 @@
         <v>182</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4957</v>
+        <v>-0.4517</v>
       </c>
       <c r="N30" t="n">
         <v>297</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.004</v>
+        <v>-0.0247</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0012</v>
+        <v>-0.0073</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6398</v>
+        <v>-0.6354</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.004</v>
+        <v>-0.0247</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.004</v>
+        <v>-0.0247</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.004</v>
+        <v>-0.0247</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.004</v>
+        <v>-0.0247</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.004</v>
+        <v>-0.0247</v>
       </c>
       <c r="N31" t="n">
         <v>89</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0546</v>
+        <v>-0.1039</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0162</v>
+        <v>-0.0309</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6627</v>
+        <v>-0.6715</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0546</v>
+        <v>-0.1039</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0546</v>
+        <v>-0.1039</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0546</v>
+        <v>-0.1039</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0546</v>
+        <v>-0.1039</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0546</v>
+        <v>-0.1039</v>
       </c>
       <c r="N32" t="n">
         <v>72</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.1314</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.029</v>
+        <v>-0.039</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6821</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.1314</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.1314</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.1314</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.1314</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.09760000000000001</v>
+        <v>-0.1314</v>
       </c>
       <c r="N33" t="n">
         <v>72</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1196</v>
+        <v>-0.1345</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0355</v>
+        <v>-0.0399</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.6854</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1196</v>
+        <v>-0.1345</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1196</v>
+        <v>-0.1345</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1196</v>
+        <v>-0.1345</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1196</v>
+        <v>-0.1345</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1196</v>
+        <v>-0.1345</v>
       </c>
       <c r="N34" t="n">
         <v>84</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3839</v>
+        <v>-0.4206</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.114</v>
+        <v>-0.1249</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8113</v>
+        <v>-0.8157</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3839</v>
+        <v>-0.4206</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.3839</v>
+        <v>-0.4206</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3839</v>
+        <v>-0.4206</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3839</v>
+        <v>-0.4206</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.3839</v>
+        <v>-0.4206</v>
       </c>
       <c r="N35" t="n">
         <v>72</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4616</v>
+        <v>-0.5375</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1371</v>
+        <v>-0.1596</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8464</v>
+        <v>-0.8689</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4616</v>
+        <v>-0.5375</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4616</v>
+        <v>-0.5375</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4616</v>
+        <v>-0.5375</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4616</v>
+        <v>-0.5375</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4616</v>
+        <v>-0.5375</v>
       </c>
       <c r="N36" t="n">
         <v>134</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.6886</v>
+        <v>-0.7304</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2045</v>
+        <v>-0.2169</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9489</v>
+        <v>-0.9567</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6886</v>
+        <v>-0.7304</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6886</v>
+        <v>-0.7304</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6886</v>
+        <v>-0.7304</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6886</v>
+        <v>-0.7304</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.6886</v>
+        <v>-0.7304</v>
       </c>
       <c r="N37" t="n">
         <v>84</v>
@@ -2148,185 +2148,185 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.008</v>
+        <v>-0.9589</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2994</v>
+        <v>-0.2848</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0931</v>
+        <v>-1.0607</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.008</v>
+        <v>-0.9589</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.008</v>
+        <v>-2.6747</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1.7158</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.008</v>
+        <v>-2.6747</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.008</v>
+        <v>-1.4443</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1.7158</v>
       </c>
       <c r="K38" t="n">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.008</v>
+        <v>0.2715000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>134</v>
+        <v>264</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2367</v>
+        <v>-1.0163</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3673</v>
+        <v>-0.3018</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1963</v>
+        <v>-1.0868</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2367</v>
+        <v>-1.0163</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6209</v>
+        <v>-1.0163</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3842</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6209</v>
+        <v>-1.0163</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8428</v>
+        <v>-1.0163</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3842</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="L39" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.4586</v>
+        <v>-1.0163</v>
       </c>
       <c r="N39" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PKL</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2759</v>
+        <v>-1.0356</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3789</v>
+        <v>-0.3076</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.214</v>
+        <v>-1.0956</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2759</v>
+        <v>-1.0356</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2759</v>
+        <v>-1.4378</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>0.4022</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2759</v>
+        <v>-1.4378</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2759</v>
+        <v>-0.7764</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>0.4022</v>
       </c>
       <c r="K40" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2759</v>
+        <v>-0.3742</v>
       </c>
       <c r="N40" t="n">
-        <v>72</v>
+        <v>132</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>PKL</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4275</v>
+        <v>-1.3012</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4239</v>
+        <v>-0.3864</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2825</v>
+        <v>-1.2165</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4275</v>
+        <v>-1.3012</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.9783</v>
+        <v>-1.3012</v>
       </c>
       <c r="G41" t="n">
-        <v>1.5508</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.9783</v>
+        <v>-1.3012</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.5486</v>
+        <v>-1.3012</v>
       </c>
       <c r="J41" t="n">
-        <v>1.5508</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="L41" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.00219999999999998</v>
+        <v>-1.3012</v>
       </c>
       <c r="N41" t="n">
-        <v>264</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5642</v>
+        <v>0.5665</v>
       </c>
       <c r="J2" t="n">
-        <v>16.926</v>
+        <v>16.995</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.26</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3648</v>
+        <v>0.3775</v>
       </c>
       <c r="J3" t="n">
-        <v>10.944</v>
+        <v>11.325</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.18</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2656</v>
+        <v>0.2812</v>
       </c>
       <c r="J4" t="n">
-        <v>7.968</v>
+        <v>8.436</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0704</v>
+        <v>0.0835</v>
       </c>
       <c r="J5" t="n">
-        <v>2.112</v>
+        <v>2.505</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.67</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3762</v>
+        <v>-0.3843</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.286</v>
+        <v>-11.529</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.474</v>
+        <v>0.4692</v>
       </c>
       <c r="J7" t="n">
-        <v>14.22</v>
+        <v>14.076</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2356</v>
+        <v>0.2434</v>
       </c>
       <c r="J8" t="n">
-        <v>7.068</v>
+        <v>7.302</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0355</v>
+        <v>-0.0423</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.065</v>
+        <v>-1.269</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.83</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2079</v>
+        <v>-0.2217</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.237</v>
+        <v>-6.651</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3069</v>
+        <v>-0.3193</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.207000000000001</v>
+        <v>-9.579000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2283</v>
+        <v>0.2345</v>
       </c>
       <c r="J12" t="n">
-        <v>9.132</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1859</v>
+        <v>0.1932</v>
       </c>
       <c r="J13" t="n">
-        <v>7.436</v>
+        <v>7.728</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0011</v>
+        <v>0.0007</v>
       </c>
       <c r="J14" t="n">
-        <v>0.044</v>
+        <v>0.028</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.0853</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.996</v>
+        <v>-3.412</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1972</v>
+        <v>-0.211</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.888</v>
+        <v>-8.44</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.33</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8759</v>
+        <v>0.8227</v>
       </c>
       <c r="J17" t="n">
-        <v>35.036</v>
+        <v>32.908</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.3</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8062</v>
+        <v>0.7617</v>
       </c>
       <c r="J18" t="n">
-        <v>32.248</v>
+        <v>30.468</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3121</v>
+        <v>0.3169</v>
       </c>
       <c r="J19" t="n">
-        <v>12.484</v>
+        <v>12.676</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2838</v>
+        <v>0.2906</v>
       </c>
       <c r="J20" t="n">
-        <v>11.352</v>
+        <v>11.624</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1712</v>
+        <v>-0.164</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.848</v>
+        <v>-6.56</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.58</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0342</v>
+        <v>0.9967</v>
       </c>
       <c r="J22" t="n">
-        <v>37.2312</v>
+        <v>35.8812</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2764</v>
+        <v>0.2836</v>
       </c>
       <c r="J23" t="n">
-        <v>9.9504</v>
+        <v>10.2096</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.99</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0242</v>
+        <v>-0.028</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8712</v>
+        <v>-1.008</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.82</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2236</v>
+        <v>-0.2361</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.0496</v>
+        <v>-8.499599999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3408</v>
+        <v>-0.3513</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.2688</v>
+        <v>-12.6468</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1694</v>
+        <v>1.173</v>
       </c>
       <c r="J27" t="n">
-        <v>42.0984</v>
+        <v>42.228</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.32</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8746</v>
+        <v>0.8177</v>
       </c>
       <c r="J28" t="n">
-        <v>31.4856</v>
+        <v>29.4372</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.7972</v>
+        <v>-2.7144</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2564</v>
+        <v>-0.2494</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.230399999999999</v>
+        <v>-8.978400000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7773</v>
+        <v>-0.7201</v>
       </c>
       <c r="J31" t="n">
-        <v>-27.9828</v>
+        <v>-25.9236</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5425</v>
+        <v>0.5881</v>
       </c>
       <c r="J32" t="n">
-        <v>12.4775</v>
+        <v>13.5263</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.77</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2409</v>
+        <v>-0.2602</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.5407</v>
+        <v>-5.9846</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.75</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2592</v>
+        <v>-0.2783</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.9616</v>
+        <v>-6.4009</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.58</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.419</v>
+        <v>-0.4322</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.637</v>
+        <v>-9.9406</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.48</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5118</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.7714</v>
+        <v>-11.9531</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>2.16</v>
       </c>
       <c r="I37" t="n">
-        <v>1.6144</v>
+        <v>1.748</v>
       </c>
       <c r="J37" t="n">
-        <v>37.1312</v>
+        <v>40.204</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.43</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7528</v>
+        <v>0.8381</v>
       </c>
       <c r="J38" t="n">
-        <v>17.3144</v>
+        <v>19.2763</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.4072</v>
+        <v>0.453</v>
       </c>
       <c r="J39" t="n">
-        <v>9.365600000000001</v>
+        <v>10.419</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.09</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2417</v>
+        <v>0.2613</v>
       </c>
       <c r="J40" t="n">
-        <v>5.5591</v>
+        <v>6.0099</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.601</v>
+        <v>-0.5533</v>
       </c>
       <c r="J41" t="n">
-        <v>-13.823</v>
+        <v>-12.7259</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2416</v>
+        <v>0.2391</v>
       </c>
       <c r="J42" t="n">
-        <v>6.5232</v>
+        <v>6.4557</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0767</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.0709</v>
+        <v>-2.4381</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1004</v>
+        <v>-0.1151</v>
       </c>
       <c r="J44" t="n">
-        <v>-2.7108</v>
+        <v>-3.1077</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2831</v>
+        <v>-0.2988</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.6437</v>
+        <v>-8.067600000000001</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3024</v>
+        <v>-0.3176</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.1648</v>
+        <v>-8.575200000000001</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.42</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7593</v>
+        <v>0.841</v>
       </c>
       <c r="J47" t="n">
-        <v>20.5011</v>
+        <v>22.707</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.29</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5876</v>
+        <v>0.653</v>
       </c>
       <c r="J48" t="n">
-        <v>15.8652</v>
+        <v>17.631</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.25</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5335</v>
+        <v>0.5927</v>
       </c>
       <c r="J49" t="n">
-        <v>14.4045</v>
+        <v>16.0029</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.11</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3231</v>
+        <v>0.3321</v>
       </c>
       <c r="J50" t="n">
-        <v>8.723699999999999</v>
+        <v>8.966699999999999</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1464</v>
+        <v>0.1654</v>
       </c>
       <c r="J51" t="n">
-        <v>3.9528</v>
+        <v>4.4658</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1288</v>
+        <v>0.1338</v>
       </c>
       <c r="J52" t="n">
-        <v>3.6064</v>
+        <v>3.7464</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1039</v>
+        <v>0.1087</v>
       </c>
       <c r="J53" t="n">
-        <v>2.9092</v>
+        <v>3.0436</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1059</v>
+        <v>-0.1192</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.9652</v>
+        <v>-3.3376</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.91</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1171</v>
+        <v>-0.1309</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.2788</v>
+        <v>-3.6652</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.82</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2122</v>
+        <v>-0.2272</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.9416</v>
+        <v>-6.3616</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.64</v>
       </c>
       <c r="I57" t="n">
-        <v>1.0568</v>
+        <v>1.1563</v>
       </c>
       <c r="J57" t="n">
-        <v>29.5904</v>
+        <v>32.3764</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.21</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4857</v>
+        <v>0.537</v>
       </c>
       <c r="J58" t="n">
-        <v>13.5996</v>
+        <v>15.036</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.08</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2544</v>
+        <v>0.2633</v>
       </c>
       <c r="J59" t="n">
-        <v>7.1232</v>
+        <v>7.3724</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0384</v>
+        <v>-0.0265</v>
       </c>
       <c r="J60" t="n">
-        <v>-1.0752</v>
+        <v>-0.742</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4783</v>
+        <v>-0.4506</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.3924</v>
+        <v>-12.6168</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.63</v>
       </c>
       <c r="I62" t="n">
-        <v>0.5796</v>
+        <v>0.6653</v>
       </c>
       <c r="J62" t="n">
-        <v>13.3308</v>
+        <v>15.3019</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.51</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5046</v>
+        <v>0.5778</v>
       </c>
       <c r="J63" t="n">
-        <v>11.6058</v>
+        <v>13.2894</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.16</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2267</v>
+        <v>0.2461</v>
       </c>
       <c r="J64" t="n">
-        <v>5.2141</v>
+        <v>5.6603</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0697</v>
+        <v>0.0878</v>
       </c>
       <c r="J65" t="n">
-        <v>1.6031</v>
+        <v>2.0194</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1261</v>
+        <v>-0.1318</v>
       </c>
       <c r="J66" t="n">
-        <v>-2.9003</v>
+        <v>-3.0314</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.98</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0037</v>
+        <v>-0.0177</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.0851</v>
+        <v>-0.4071</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.97</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0188</v>
+        <v>-0.034</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.4324</v>
+        <v>-0.782</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.84</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.174</v>
+        <v>-0.1932</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.002</v>
+        <v>-4.4436</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.72</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2893</v>
+        <v>-0.3074</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.6539</v>
+        <v>-7.0702</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.41</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5779</v>
+        <v>-0.5812</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.2917</v>
+        <v>-13.3676</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2106</v>
+        <v>0.2057</v>
       </c>
       <c r="J72" t="n">
-        <v>5.265</v>
+        <v>5.1425</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.01</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0788</v>
+        <v>0.0731</v>
       </c>
       <c r="J73" t="n">
-        <v>1.97</v>
+        <v>1.8275</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.8</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.22</v>
+        <v>-0.2376</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.5</v>
+        <v>-5.94</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.74</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2784</v>
+        <v>-0.2951</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.96</v>
+        <v>-7.3775</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.61</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4015</v>
+        <v>-0.4138</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.0375</v>
+        <v>-10.345</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.56</v>
       </c>
       <c r="I77" t="n">
-        <v>0.9484</v>
+        <v>1.0425</v>
       </c>
       <c r="J77" t="n">
-        <v>23.71</v>
+        <v>26.0625</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.23</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5107</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="J78" t="n">
-        <v>12.7675</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3307</v>
+        <v>0.3385</v>
       </c>
       <c r="J79" t="n">
-        <v>8.2675</v>
+        <v>8.4625</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0885</v>
+        <v>0.1069</v>
       </c>
       <c r="J80" t="n">
-        <v>2.2125</v>
+        <v>2.6725</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.99</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.09950000000000001</v>
+        <v>-0.0906</v>
       </c>
       <c r="J81" t="n">
-        <v>-2.4875</v>
+        <v>-2.265</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.8</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4673</v>
+        <v>1.4577</v>
       </c>
       <c r="J82" t="n">
-        <v>35.2152</v>
+        <v>34.9848</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.78</v>
       </c>
       <c r="I83" t="n">
-        <v>1.444</v>
+        <v>1.433</v>
       </c>
       <c r="J83" t="n">
-        <v>34.656</v>
+        <v>34.392</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.52</v>
       </c>
       <c r="I84" t="n">
-        <v>1.1336</v>
+        <v>1.1023</v>
       </c>
       <c r="J84" t="n">
-        <v>27.2064</v>
+        <v>26.4552</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5253</v>
+        <v>-0.4837</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.6072</v>
+        <v>-11.6088</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5796</v>
+        <v>-0.5329</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.9104</v>
+        <v>-12.7896</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.87</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1216</v>
+        <v>-0.1452</v>
       </c>
       <c r="J87" t="n">
-        <v>-2.9184</v>
+        <v>-3.4848</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.82</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.1775</v>
+        <v>-0.2004</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.26</v>
+        <v>-4.8096</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.76</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2398</v>
+        <v>-0.2615</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.7552</v>
+        <v>-6.276</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.63</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3603</v>
+        <v>-0.3784</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.6472</v>
+        <v>-9.0816</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5846</v>
+        <v>-0.589</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.0304</v>
+        <v>-14.136</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.51</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1573</v>
+        <v>1.1206</v>
       </c>
       <c r="J92" t="n">
-        <v>31.2471</v>
+        <v>30.2562</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.633</v>
+        <v>0.6103</v>
       </c>
       <c r="J93" t="n">
-        <v>17.091</v>
+        <v>16.4781</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.15</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4395</v>
+        <v>0.4352</v>
       </c>
       <c r="J94" t="n">
-        <v>11.8665</v>
+        <v>11.7504</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1222</v>
+        <v>0.1399</v>
       </c>
       <c r="J95" t="n">
-        <v>3.2994</v>
+        <v>3.7773</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.01</v>
       </c>
       <c r="I96" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0284</v>
       </c>
       <c r="J96" t="n">
-        <v>0.2511</v>
+        <v>0.7668</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.29</v>
       </c>
       <c r="I97" t="n">
-        <v>0.621</v>
+        <v>0.5972</v>
       </c>
       <c r="J97" t="n">
-        <v>16.767</v>
+        <v>16.1244</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2609</v>
+        <v>0.263</v>
       </c>
       <c r="J98" t="n">
-        <v>7.0443</v>
+        <v>7.101</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1063</v>
+        <v>-0.1195</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.8701</v>
+        <v>-3.2265</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.87</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1609</v>
+        <v>-0.1756</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.3443</v>
+        <v>-4.7412</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4602</v>
+        <v>-0.4677</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.4254</v>
+        <v>-12.6279</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.11</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3661</v>
+        <v>0.345</v>
       </c>
       <c r="J102" t="n">
-        <v>8.420299999999999</v>
+        <v>7.935</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0413</v>
+        <v>-0.0593</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.9499</v>
+        <v>-1.3639</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.88</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1266</v>
+        <v>-0.1466</v>
       </c>
       <c r="J104" t="n">
-        <v>-2.9118</v>
+        <v>-3.3718</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.47</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5199</v>
+        <v>-0.5275</v>
       </c>
       <c r="J105" t="n">
-        <v>-11.9577</v>
+        <v>-12.1325</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.4</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5844</v>
+        <v>-0.5876</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.4412</v>
+        <v>-13.5148</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.71</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3518</v>
+        <v>1.3373</v>
       </c>
       <c r="J107" t="n">
-        <v>31.0914</v>
+        <v>30.7579</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.67</v>
       </c>
       <c r="I108" t="n">
-        <v>1.3049</v>
+        <v>1.2874</v>
       </c>
       <c r="J108" t="n">
-        <v>30.0127</v>
+        <v>29.6102</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.5</v>
       </c>
       <c r="I109" t="n">
-        <v>1.1025</v>
+        <v>1.0699</v>
       </c>
       <c r="J109" t="n">
-        <v>25.3575</v>
+        <v>24.6077</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.23</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5906</v>
+        <v>0.5812</v>
       </c>
       <c r="J110" t="n">
-        <v>13.5838</v>
+        <v>13.3676</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2986</v>
+        <v>-0.2712</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.8678</v>
+        <v>-6.2376</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7728</v>
+        <v>0.7375</v>
       </c>
       <c r="J112" t="n">
-        <v>21.6384</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1845</v>
+        <v>0.1922</v>
       </c>
       <c r="J113" t="n">
-        <v>5.166</v>
+        <v>5.3816</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0383</v>
+        <v>0.0437</v>
       </c>
       <c r="J114" t="n">
-        <v>1.0724</v>
+        <v>1.2236</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2082</v>
+        <v>-0.2218</v>
       </c>
       <c r="J115" t="n">
-        <v>-5.8296</v>
+        <v>-6.2104</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3547</v>
+        <v>-0.3656</v>
       </c>
       <c r="J116" t="n">
-        <v>-9.9316</v>
+        <v>-10.2368</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9197</v>
+        <v>0.8617</v>
       </c>
       <c r="J117" t="n">
-        <v>25.7516</v>
+        <v>24.1276</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.657</v>
       </c>
       <c r="J118" t="n">
-        <v>19.236</v>
+        <v>18.396</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5666</v>
+        <v>0.5496</v>
       </c>
       <c r="J119" t="n">
-        <v>15.8648</v>
+        <v>15.3888</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.03</v>
       </c>
       <c r="I120" t="n">
-        <v>0.094</v>
+        <v>0.1108</v>
       </c>
       <c r="J120" t="n">
-        <v>2.632</v>
+        <v>3.1024</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.98</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.135</v>
+        <v>-0.1281</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.78</v>
+        <v>-3.5868</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.23</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6965</v>
+        <v>0.6544</v>
       </c>
       <c r="J122" t="n">
-        <v>20.895</v>
+        <v>19.632</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.22</v>
       </c>
       <c r="I123" t="n">
-        <v>0.671</v>
+        <v>0.6319</v>
       </c>
       <c r="J123" t="n">
-        <v>20.13</v>
+        <v>18.957</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.95</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1983</v>
+        <v>-0.201</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.949</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4624</v>
+        <v>-0.4451</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.872</v>
+        <v>-13.353</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.76</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.7251</v>
+        <v>-0.679</v>
       </c>
       <c r="J126" t="n">
-        <v>-21.753</v>
+        <v>-20.37</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4965</v>
+        <v>0.4899</v>
       </c>
       <c r="J127" t="n">
-        <v>14.895</v>
+        <v>14.697</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.256</v>
+        <v>0.2642</v>
       </c>
       <c r="J128" t="n">
-        <v>7.68</v>
+        <v>7.926</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1319</v>
+        <v>0.1426</v>
       </c>
       <c r="J129" t="n">
-        <v>3.957</v>
+        <v>4.278</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.99</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0245</v>
+        <v>-0.0283</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.735</v>
+        <v>-0.849</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.84</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2036</v>
+        <v>-0.216</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.108</v>
+        <v>-6.48</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.29</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7867</v>
+        <v>0.7439</v>
       </c>
       <c r="J132" t="n">
-        <v>20.4542</v>
+        <v>19.3414</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.24</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6676</v>
+        <v>0.6389</v>
       </c>
       <c r="J133" t="n">
-        <v>17.3576</v>
+        <v>16.6114</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.21</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5948</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="J134" t="n">
-        <v>15.4648</v>
+        <v>14.9266</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1973</v>
+        <v>0.2088</v>
       </c>
       <c r="J135" t="n">
-        <v>5.1298</v>
+        <v>5.4288</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3</v>
+        <v>-0.2874</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.8</v>
+        <v>-7.4724</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.16</v>
       </c>
       <c r="I137" t="n">
-        <v>0.3845</v>
+        <v>0.379</v>
       </c>
       <c r="J137" t="n">
-        <v>9.997</v>
+        <v>9.853999999999999</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.13</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3253</v>
+        <v>0.3235</v>
       </c>
       <c r="J138" t="n">
-        <v>8.457800000000001</v>
+        <v>8.411</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.87</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1598</v>
+        <v>-0.1747</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.1548</v>
+        <v>-4.5422</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2115</v>
+        <v>-0.2266</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.499</v>
+        <v>-5.8916</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3194</v>
+        <v>-0.3327</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.304399999999999</v>
+        <v>-8.6502</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.19</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4604</v>
+        <v>0.446</v>
       </c>
       <c r="J142" t="n">
-        <v>11.51</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0915</v>
+        <v>0.0917</v>
       </c>
       <c r="J143" t="n">
-        <v>2.2875</v>
+        <v>2.2925</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1757</v>
+        <v>-0.192</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.3925</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2261</v>
+        <v>-0.2424</v>
       </c>
       <c r="J145" t="n">
-        <v>-5.6525</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.408</v>
+        <v>-0.4189</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.2</v>
+        <v>-10.4725</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2763</v>
+        <v>1.2468</v>
       </c>
       <c r="J147" t="n">
-        <v>31.9075</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.6606</v>
+        <v>0.634</v>
       </c>
       <c r="J148" t="n">
-        <v>16.515</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.13</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3907</v>
+        <v>0.3899</v>
       </c>
       <c r="J149" t="n">
-        <v>9.7675</v>
+        <v>9.7475</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.07</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2217</v>
+        <v>0.2334</v>
       </c>
       <c r="J150" t="n">
-        <v>5.5425</v>
+        <v>5.835</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.82</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6162</v>
+        <v>-0.5741000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-15.405</v>
+        <v>-14.3525</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0323</v>
+        <v>0.0076</v>
       </c>
       <c r="J152" t="n">
-        <v>0.6137</v>
+        <v>0.1444</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0554</v>
+        <v>-0.0737</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.0526</v>
+        <v>-1.4003</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.79</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2217</v>
+        <v>-0.2413</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.2123</v>
+        <v>-4.5847</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.64</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3622</v>
+        <v>-0.3782</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.8818</v>
+        <v>-7.1858</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.47</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5205</v>
+        <v>-0.5279</v>
       </c>
       <c r="J156" t="n">
-        <v>-9.8895</v>
+        <v>-10.0301</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.57</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1886</v>
+        <v>1.1626</v>
       </c>
       <c r="J157" t="n">
-        <v>22.5834</v>
+        <v>22.0894</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.43</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0147</v>
+        <v>0.9678</v>
       </c>
       <c r="J158" t="n">
-        <v>19.2793</v>
+        <v>18.3882</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.37</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9091</v>
+        <v>0.8623</v>
       </c>
       <c r="J159" t="n">
-        <v>17.2729</v>
+        <v>16.3837</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.34</v>
       </c>
       <c r="I160" t="n">
-        <v>0.8451</v>
+        <v>0.8057</v>
       </c>
       <c r="J160" t="n">
-        <v>16.0569</v>
+        <v>15.3083</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.28</v>
       </c>
       <c r="I161" t="n">
-        <v>0.7109</v>
+        <v>0.6874</v>
       </c>
       <c r="J161" t="n">
-        <v>13.5071</v>
+        <v>13.0606</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.78</v>
       </c>
       <c r="I162" t="n">
-        <v>1.4752</v>
+        <v>1.4607</v>
       </c>
       <c r="J162" t="n">
-        <v>42.7808</v>
+        <v>42.3603</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7817</v>
+        <v>0.7448</v>
       </c>
       <c r="J163" t="n">
-        <v>22.6693</v>
+        <v>21.5992</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5764</v>
+        <v>0.5616</v>
       </c>
       <c r="J164" t="n">
-        <v>16.7156</v>
+        <v>16.2864</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.15</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4267</v>
+        <v>0.4264</v>
       </c>
       <c r="J165" t="n">
-        <v>12.3743</v>
+        <v>12.3656</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.8</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6862</v>
+        <v>-0.6332</v>
       </c>
       <c r="J166" t="n">
-        <v>-19.8998</v>
+        <v>-18.3628</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.99</v>
       </c>
       <c r="I167" t="n">
-        <v>0.006</v>
+        <v>-0.0068</v>
       </c>
       <c r="J167" t="n">
-        <v>0.174</v>
+        <v>-0.1972</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.86</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1591</v>
+        <v>-0.1768</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.6139</v>
+        <v>-5.1272</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1694</v>
+        <v>-0.1872</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.9126</v>
+        <v>-5.4288</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.76</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2567</v>
+        <v>-0.2743</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.4443</v>
+        <v>-7.9547</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3427</v>
+        <v>-0.3579</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.9383</v>
+        <v>-10.3791</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>2.07</v>
       </c>
       <c r="I172" t="n">
-        <v>1.8338</v>
+        <v>1.8379</v>
       </c>
       <c r="J172" t="n">
-        <v>51.3464</v>
+        <v>51.4612</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3313</v>
+        <v>0.3366</v>
       </c>
       <c r="J173" t="n">
-        <v>9.276400000000001</v>
+        <v>9.424799999999999</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.1851</v>
+        <v>0.2004</v>
       </c>
       <c r="J174" t="n">
-        <v>5.1828</v>
+        <v>5.6112</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.98</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1437</v>
+        <v>-0.1342</v>
       </c>
       <c r="J175" t="n">
-        <v>-4.0236</v>
+        <v>-3.7576</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7759</v>
+        <v>-0.7147</v>
       </c>
       <c r="J176" t="n">
-        <v>-21.7252</v>
+        <v>-20.0116</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.2</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4786</v>
+        <v>0.4631</v>
       </c>
       <c r="J177" t="n">
-        <v>13.4008</v>
+        <v>12.9668</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.97</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.04</v>
+        <v>-0.0505</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.12</v>
+        <v>-1.414</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.86</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1656</v>
+        <v>-0.1817</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.6368</v>
+        <v>-5.0876</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.83</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1963</v>
+        <v>-0.2126</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.4964</v>
+        <v>-5.9528</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.62</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.399</v>
+        <v>-0.4102</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.172</v>
+        <v>-11.4856</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2765</v>
+        <v>0.2744</v>
       </c>
       <c r="J182" t="n">
-        <v>7.4655</v>
+        <v>7.4088</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.92</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1028</v>
+        <v>-0.1169</v>
       </c>
       <c r="J183" t="n">
-        <v>-2.7756</v>
+        <v>-3.1563</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1244</v>
+        <v>-0.1394</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.3588</v>
+        <v>-3.7638</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.84</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1868</v>
+        <v>-0.2029</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.0436</v>
+        <v>-5.4783</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.75</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2763</v>
+        <v>-0.2916</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.4601</v>
+        <v>-7.8732</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.49</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1178</v>
+        <v>1.0808</v>
       </c>
       <c r="J187" t="n">
-        <v>30.1806</v>
+        <v>29.1816</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.34</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8714</v>
+        <v>0.8236</v>
       </c>
       <c r="J188" t="n">
-        <v>23.5278</v>
+        <v>22.2372</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6236</v>
+        <v>0.6039</v>
       </c>
       <c r="J189" t="n">
-        <v>16.8372</v>
+        <v>16.3053</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5523</v>
+        <v>0.5399</v>
       </c>
       <c r="J190" t="n">
-        <v>14.9121</v>
+        <v>14.5773</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.98</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1566</v>
+        <v>-0.1432</v>
       </c>
       <c r="J191" t="n">
-        <v>-4.2282</v>
+        <v>-3.8664</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.15</v>
       </c>
       <c r="I192" t="n">
-        <v>1.814</v>
+        <v>1.8277</v>
       </c>
       <c r="J192" t="n">
-        <v>32.652</v>
+        <v>32.8986</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.54</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1361</v>
+        <v>1.1097</v>
       </c>
       <c r="J193" t="n">
-        <v>20.4498</v>
+        <v>19.9746</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.51</v>
       </c>
       <c r="I194" t="n">
-        <v>1.1014</v>
+        <v>1.0717</v>
       </c>
       <c r="J194" t="n">
-        <v>19.8252</v>
+        <v>19.2906</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.38</v>
       </c>
       <c r="I195" t="n">
-        <v>0.9019</v>
+        <v>0.8613</v>
       </c>
       <c r="J195" t="n">
-        <v>16.2342</v>
+        <v>15.5034</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.21</v>
       </c>
       <c r="I196" t="n">
-        <v>0.5124</v>
+        <v>0.5171</v>
       </c>
       <c r="J196" t="n">
-        <v>9.2232</v>
+        <v>9.3078</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.02</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2801</v>
+        <v>0.2312</v>
       </c>
       <c r="J197" t="n">
-        <v>5.0418</v>
+        <v>4.1616</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.82</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.1437</v>
+        <v>-0.174</v>
       </c>
       <c r="J198" t="n">
-        <v>-2.5866</v>
+        <v>-3.132</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.55</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4162</v>
+        <v>-0.4347</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.4916</v>
+        <v>-7.8246</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.41</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5481</v>
+        <v>-0.5577</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.8658</v>
+        <v>-10.0386</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.14</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.8098</v>
+        <v>-0.7964</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.5764</v>
+        <v>-14.3352</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.85</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4885</v>
+        <v>1.4862</v>
       </c>
       <c r="J202" t="n">
-        <v>29.77</v>
+        <v>29.724</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.5</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0914</v>
+        <v>1.0601</v>
       </c>
       <c r="J203" t="n">
-        <v>21.828</v>
+        <v>21.202</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.47</v>
       </c>
       <c r="I204" t="n">
-        <v>1.0555</v>
+        <v>1.0183</v>
       </c>
       <c r="J204" t="n">
-        <v>21.11</v>
+        <v>20.366</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.46</v>
       </c>
       <c r="I205" t="n">
-        <v>1.0428</v>
+        <v>1.0032</v>
       </c>
       <c r="J205" t="n">
-        <v>20.856</v>
+        <v>20.064</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.41</v>
       </c>
       <c r="I206" t="n">
-        <v>0.965</v>
+        <v>0.9195</v>
       </c>
       <c r="J206" t="n">
-        <v>19.3</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.92</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0295</v>
+        <v>-0.0594</v>
       </c>
       <c r="J207" t="n">
-        <v>-0.59</v>
+        <v>-1.188</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.76</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2188</v>
+        <v>-0.2451</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.376</v>
+        <v>-4.902</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.67</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3111</v>
+        <v>-0.3336</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.222</v>
+        <v>-6.672</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.42</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5427</v>
+        <v>-0.5521</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.854</v>
+        <v>-11.042</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.28</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6768</v>
+        <v>-0.6753</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.536</v>
+        <v>-13.506</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.73</v>
       </c>
       <c r="I212" t="n">
-        <v>1.4189</v>
+        <v>1.4008</v>
       </c>
       <c r="J212" t="n">
-        <v>39.7292</v>
+        <v>39.2224</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.53</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1714</v>
+        <v>1.1379</v>
       </c>
       <c r="J213" t="n">
-        <v>32.7992</v>
+        <v>31.8612</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.08</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2367</v>
+        <v>0.251</v>
       </c>
       <c r="J214" t="n">
-        <v>6.6276</v>
+        <v>7.028</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.99</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.112</v>
+        <v>-0.0993</v>
       </c>
       <c r="J215" t="n">
-        <v>-3.136</v>
+        <v>-2.7804</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5782</v>
+        <v>-0.5372</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.1896</v>
+        <v>-15.0416</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.23</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5412</v>
+        <v>0.5194</v>
       </c>
       <c r="J217" t="n">
-        <v>15.1536</v>
+        <v>14.5432</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.15</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3863</v>
+        <v>0.3765</v>
       </c>
       <c r="J218" t="n">
-        <v>10.8164</v>
+        <v>10.542</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1337</v>
+        <v>-0.1494</v>
       </c>
       <c r="J219" t="n">
-        <v>-3.7436</v>
+        <v>-4.1832</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.73</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2933</v>
+        <v>-0.3086</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.212400000000001</v>
+        <v>-8.6408</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.42</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5797</v>
+        <v>-0.5813</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.2316</v>
+        <v>-16.2764</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3313/event_3313_evp_summary.xlsx
+++ b/database/event/3313/event_3313_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.1551</v>
+        <v>6.2649</v>
       </c>
       <c r="C2" t="n">
-        <v>1.828</v>
+        <v>1.8606</v>
       </c>
       <c r="D2" t="n">
-        <v>2.1777</v>
+        <v>2.2482</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1551</v>
+        <v>6.2649</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4501</v>
+        <v>2.5269</v>
       </c>
       <c r="G2" t="n">
-        <v>3.705</v>
+        <v>3.738</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1895</v>
+        <v>3.0443</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7223</v>
+        <v>1.7093</v>
       </c>
       <c r="J2" t="n">
-        <v>3.705</v>
+        <v>3.738</v>
       </c>
       <c r="K2" t="n">
         <v>108</v>
@@ -529,7 +529,7 @@
         <v>156</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4273</v>
+        <v>5.4473</v>
       </c>
       <c r="N2" t="n">
         <v>264</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2905</v>
+        <v>5.3642</v>
       </c>
       <c r="C3" t="n">
-        <v>1.5712</v>
+        <v>1.5931</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7841</v>
+        <v>1.8379</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2905</v>
+        <v>5.3642</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2737</v>
+        <v>2.4203</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0168</v>
+        <v>2.9439</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6076</v>
+        <v>2.6441</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4081</v>
+        <v>1.4846</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0168</v>
+        <v>2.9439</v>
       </c>
       <c r="K3" t="n">
         <v>115</v>
@@ -575,7 +575,7 @@
         <v>182</v>
       </c>
       <c r="M3" t="n">
-        <v>4.4249</v>
+        <v>4.4285</v>
       </c>
       <c r="N3" t="n">
         <v>297</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4926</v>
+        <v>4.4072</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3342</v>
+        <v>1.3089</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4209</v>
+        <v>1.4019</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4926</v>
+        <v>4.4072</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7588</v>
+        <v>3.6899</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7338</v>
+        <v>0.7173</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5075</v>
+        <v>7.4107</v>
       </c>
       <c r="I4" t="n">
-        <v>4.054</v>
+        <v>4.1609</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7338</v>
+        <v>0.7173</v>
       </c>
       <c r="K4" t="n">
         <v>108</v>
@@ -621,7 +621,7 @@
         <v>156</v>
       </c>
       <c r="M4" t="n">
-        <v>4.787800000000001</v>
+        <v>4.8782</v>
       </c>
       <c r="N4" t="n">
         <v>264</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1755</v>
+        <v>3.9716</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2401</v>
+        <v>1.1795</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2766</v>
+        <v>1.2035</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1755</v>
+        <v>3.9716</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0858</v>
+        <v>3.0465</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0897</v>
+        <v>0.9251</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2869</v>
+        <v>4.9951</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8549</v>
+        <v>2.8046</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0897</v>
+        <v>0.9251</v>
       </c>
       <c r="K5" t="n">
         <v>115</v>
@@ -667,7 +667,7 @@
         <v>182</v>
       </c>
       <c r="M5" t="n">
-        <v>3.9446</v>
+        <v>3.7297</v>
       </c>
       <c r="N5" t="n">
         <v>297</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.8585</v>
+        <v>3.7807</v>
       </c>
       <c r="C6" t="n">
-        <v>1.1459</v>
+        <v>1.1228</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1323</v>
+        <v>1.1165</v>
       </c>
       <c r="E6" t="n">
-        <v>3.8585</v>
+        <v>3.7807</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0545</v>
+        <v>3.0299</v>
       </c>
       <c r="G6" t="n">
-        <v>0.804</v>
+        <v>0.7508</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1838</v>
+        <v>4.9328</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7992</v>
+        <v>2.7696</v>
       </c>
       <c r="J6" t="n">
-        <v>0.804</v>
+        <v>0.7508</v>
       </c>
       <c r="K6" t="n">
         <v>115</v>
@@ -713,7 +713,7 @@
         <v>182</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6032</v>
+        <v>3.5204</v>
       </c>
       <c r="N6" t="n">
         <v>297</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3173</v>
+        <v>3.4278</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9852</v>
+        <v>1.018</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8859</v>
+        <v>0.9557</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3173</v>
+        <v>3.4278</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3679</v>
+        <v>2.4811</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9494</v>
+        <v>0.9467</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9184</v>
+        <v>2.8725</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5759</v>
+        <v>1.6128</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9494</v>
+        <v>0.9467</v>
       </c>
       <c r="K7" t="n">
         <v>108</v>
@@ -759,7 +759,7 @@
         <v>156</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5253</v>
+        <v>2.5595</v>
       </c>
       <c r="N7" t="n">
         <v>264</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2986</v>
+        <v>3.2278</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9796</v>
+        <v>0.9586</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8774</v>
+        <v>0.8646</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2986</v>
+        <v>3.2278</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1327</v>
+        <v>3.0813</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1659</v>
+        <v>0.1465</v>
       </c>
       <c r="H8" t="n">
-        <v>5.4418</v>
+        <v>5.1258</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9385</v>
+        <v>2.878</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1659</v>
+        <v>0.1465</v>
       </c>
       <c r="K8" t="n">
         <v>115</v>
@@ -805,7 +805,7 @@
         <v>182</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1044</v>
+        <v>3.0245</v>
       </c>
       <c r="N8" t="n">
         <v>297</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8273</v>
+        <v>2.8861</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8397</v>
+        <v>0.8571</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.709</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8273</v>
+        <v>2.8861</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6063</v>
+        <v>2.6646</v>
       </c>
       <c r="G9" t="n">
-        <v>0.221</v>
+        <v>0.2215</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7049</v>
+        <v>3.5616</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0006</v>
+        <v>1.9997</v>
       </c>
       <c r="J9" t="n">
-        <v>0.221</v>
+        <v>0.2215</v>
       </c>
       <c r="K9" t="n">
         <v>56</v>
@@ -851,7 +851,7 @@
         <v>76</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2216</v>
+        <v>2.2212</v>
       </c>
       <c r="N9" t="n">
         <v>132</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5935</v>
+        <v>2.6267</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7702</v>
+        <v>0.7801</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5564</v>
+        <v>0.5908</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5935</v>
+        <v>2.6267</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4052</v>
+        <v>2.4849</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1883</v>
+        <v>0.1418</v>
       </c>
       <c r="H10" t="n">
-        <v>3.0415</v>
+        <v>2.8867</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6424</v>
+        <v>1.6208</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1883</v>
+        <v>0.1418</v>
       </c>
       <c r="K10" t="n">
         <v>56</v>
@@ -897,7 +897,7 @@
         <v>76</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8307</v>
+        <v>1.7626</v>
       </c>
       <c r="N10" t="n">
         <v>132</v>
@@ -906,81 +906,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2933</v>
+        <v>2.3729</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6811</v>
+        <v>0.7047</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4198</v>
+        <v>0.4752</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2933</v>
+        <v>2.3729</v>
       </c>
       <c r="F11" t="n">
-        <v>1.908</v>
+        <v>2.7161</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3853</v>
+        <v>-0.3432</v>
       </c>
       <c r="H11" t="n">
-        <v>1.908</v>
+        <v>3.7546</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0303</v>
+        <v>2.1081</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3853</v>
+        <v>-0.3432</v>
       </c>
       <c r="K11" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="L11" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4156</v>
+        <v>1.7649</v>
       </c>
       <c r="N11" t="n">
-        <v>132</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2748</v>
+        <v>2.3294</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6756</v>
+        <v>0.6918</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4113</v>
+        <v>0.4554</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2748</v>
+        <v>2.3294</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6501</v>
+        <v>2.6678</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3753</v>
+        <v>-0.3384</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8495</v>
+        <v>3.5735</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0787</v>
+        <v>2.0064</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3753</v>
+        <v>-0.3384</v>
       </c>
       <c r="K12" t="n">
         <v>46</v>
@@ -989,7 +989,7 @@
         <v>50</v>
       </c>
       <c r="M12" t="n">
-        <v>1.7034</v>
+        <v>1.668</v>
       </c>
       <c r="N12" t="n">
         <v>96</v>
@@ -998,35 +998,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>JW</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2369</v>
+        <v>2.0755</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6643</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3941</v>
+        <v>0.3397</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2369</v>
+        <v>2.0755</v>
       </c>
       <c r="F13" t="n">
-        <v>2.6055</v>
+        <v>1.8012</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3686</v>
+        <v>0.2743</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7023</v>
+        <v>1.8012</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9992</v>
+        <v>1.0113</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3686</v>
+        <v>0.2743</v>
       </c>
       <c r="K13" t="n">
         <v>46</v>
@@ -1035,7 +1035,7 @@
         <v>50</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6306</v>
+        <v>1.2856</v>
       </c>
       <c r="N13" t="n">
         <v>96</v>
@@ -1044,47 +1044,47 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JW</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0713</v>
+        <v>2.0419</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6151</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3187</v>
+        <v>0.3244</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0713</v>
+        <v>2.0419</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8008</v>
+        <v>1.7221</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2705</v>
+        <v>0.3198</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8008</v>
+        <v>1.7221</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9724</v>
+        <v>0.9669</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2705</v>
+        <v>0.3198</v>
       </c>
       <c r="K14" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L14" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2429</v>
+        <v>1.2867</v>
       </c>
       <c r="N14" t="n">
-        <v>96</v>
+        <v>132</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8289</v>
+        <v>1.9206</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5432</v>
+        <v>0.5704</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2083</v>
+        <v>0.2691</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8289</v>
+        <v>1.9206</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5599</v>
+        <v>2.6249</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.731</v>
+        <v>-0.7043</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5517</v>
+        <v>3.4123</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9179</v>
+        <v>1.9159</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.731</v>
+        <v>-0.7043</v>
       </c>
       <c r="K15" t="n">
         <v>46</v>
@@ -1127,7 +1127,7 @@
         <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1869</v>
+        <v>1.2116</v>
       </c>
       <c r="N15" t="n">
         <v>96</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7096</v>
+        <v>1.8401</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5077</v>
+        <v>0.5465</v>
       </c>
       <c r="D16" t="n">
-        <v>0.154</v>
+        <v>0.2325</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7096</v>
+        <v>1.8401</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3637</v>
+        <v>2.4381</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6541</v>
+        <v>-0.598</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9045</v>
+        <v>2.7109</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5684</v>
+        <v>1.5221</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6541</v>
+        <v>-0.598</v>
       </c>
       <c r="K16" t="n">
         <v>56</v>
@@ -1173,7 +1173,7 @@
         <v>76</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9143</v>
+        <v>0.9241</v>
       </c>
       <c r="N16" t="n">
         <v>132</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.4237</v>
+        <v>1.3957</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4228</v>
+        <v>0.4145</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0239</v>
+        <v>0.03</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4237</v>
+        <v>1.3957</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4237</v>
+        <v>1.3957</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4237</v>
+        <v>1.3957</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4237</v>
+        <v>1.3957</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.4237</v>
+        <v>1.3957</v>
       </c>
       <c r="N17" t="n">
         <v>89</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0926</v>
+        <v>1.041</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3245</v>
+        <v>0.3092</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1268</v>
+        <v>-0.1316</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0926</v>
+        <v>1.041</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1372</v>
+        <v>-0.1546</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2298</v>
+        <v>1.1956</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1372</v>
+        <v>-0.1546</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0741</v>
+        <v>-0.0868</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2298</v>
+        <v>1.1956</v>
       </c>
       <c r="K18" t="n">
         <v>108</v>
@@ -1265,7 +1265,7 @@
         <v>156</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1557</v>
+        <v>1.1088</v>
       </c>
       <c r="N18" t="n">
         <v>264</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9142</v>
+        <v>0.8865</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2715</v>
+        <v>0.2633</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.208</v>
+        <v>-0.2019</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9142</v>
+        <v>0.8865</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9142</v>
+        <v>0.8865</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9142</v>
+        <v>0.8865</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9142</v>
+        <v>0.8865</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9142</v>
+        <v>0.8865</v>
       </c>
       <c r="N19" t="n">
         <v>89</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7796</v>
+        <v>0.7947</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2315</v>
+        <v>0.236</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2693</v>
+        <v>-0.2438</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7796</v>
+        <v>0.7947</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0602</v>
+        <v>1.1212</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2806</v>
+        <v>-0.3265</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0602</v>
+        <v>1.1212</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5725</v>
+        <v>0.6294999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2806</v>
+        <v>-0.3265</v>
       </c>
       <c r="K20" t="n">
         <v>46</v>
@@ -1357,7 +1357,7 @@
         <v>50</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2919</v>
+        <v>0.3029999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>96</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6448</v>
+        <v>0.6196</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1915</v>
+        <v>0.184</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3307</v>
+        <v>-0.3235</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6448</v>
+        <v>0.6196</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6448</v>
+        <v>0.6196</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6448</v>
+        <v>0.6196</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6448</v>
+        <v>0.6196</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6448</v>
+        <v>0.6196</v>
       </c>
       <c r="N21" t="n">
         <v>134</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6008</v>
+        <v>0.5466</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1784</v>
+        <v>0.1623</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3507</v>
+        <v>-0.3568</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6008</v>
+        <v>0.5466</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6008</v>
+        <v>0.5466</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6008</v>
+        <v>0.5466</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6008</v>
+        <v>0.5466</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6008</v>
+        <v>0.5466</v>
       </c>
       <c r="N22" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5225</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1552</v>
+        <v>0.1498</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3864</v>
+        <v>-0.376</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5225</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5225</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5225</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5225</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5225</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4697</v>
+        <v>0.3948</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1395</v>
+        <v>0.1173</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4104</v>
+        <v>-0.4259</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4697</v>
+        <v>0.3948</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4697</v>
+        <v>0.3948</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4697</v>
+        <v>0.3948</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4697</v>
+        <v>0.3948</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4697</v>
+        <v>0.3948</v>
       </c>
       <c r="N24" t="n">
         <v>134</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.33</v>
+        <v>0.3115</v>
       </c>
       <c r="C25" t="n">
-        <v>0.098</v>
+        <v>0.0925</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.474</v>
+        <v>-0.4639</v>
       </c>
       <c r="E25" t="n">
-        <v>0.33</v>
+        <v>0.3115</v>
       </c>
       <c r="F25" t="n">
-        <v>0.33</v>
+        <v>0.3115</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.33</v>
+        <v>0.3115</v>
       </c>
       <c r="I25" t="n">
-        <v>0.33</v>
+        <v>0.3115</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.33</v>
+        <v>0.3115</v>
       </c>
       <c r="N25" t="n">
-        <v>89</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3253</v>
+        <v>0.2642</v>
       </c>
       <c r="C26" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.0785</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4761</v>
+        <v>-0.4854</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3253</v>
+        <v>0.2642</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3253</v>
+        <v>0.2642</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3253</v>
+        <v>0.2642</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3253</v>
+        <v>0.2642</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3253</v>
+        <v>0.2642</v>
       </c>
       <c r="N26" t="n">
-        <v>134</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2846</v>
+        <v>0.2548</v>
       </c>
       <c r="C27" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0757</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4946</v>
+        <v>-0.4897</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2846</v>
+        <v>0.2548</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2846</v>
+        <v>0.2548</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2846</v>
+        <v>0.2548</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2846</v>
+        <v>0.2548</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2846</v>
+        <v>0.2548</v>
       </c>
       <c r="N27" t="n">
         <v>72</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2601</v>
+        <v>0.2297</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0772</v>
+        <v>0.0682</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5058</v>
+        <v>-0.5011</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2601</v>
+        <v>0.2297</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2601</v>
+        <v>0.2297</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2601</v>
+        <v>0.2297</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2601</v>
+        <v>0.2297</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2601</v>
+        <v>0.2297</v>
       </c>
       <c r="N28" t="n">
         <v>84</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.233</v>
+        <v>0.138</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0692</v>
+        <v>0.041</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5181</v>
+        <v>-0.5429</v>
       </c>
       <c r="E29" t="n">
-        <v>0.233</v>
+        <v>0.138</v>
       </c>
       <c r="F29" t="n">
-        <v>0.233</v>
+        <v>0.138</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.233</v>
+        <v>0.138</v>
       </c>
       <c r="I29" t="n">
-        <v>0.233</v>
+        <v>0.138</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.233</v>
+        <v>0.138</v>
       </c>
       <c r="N29" t="n">
         <v>84</v>
@@ -1780,124 +1780,124 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STYKO</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0639</v>
+        <v>0.0034</v>
       </c>
       <c r="C30" t="n">
-        <v>0.019</v>
+        <v>0.001</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5951</v>
+        <v>-0.6042</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0639</v>
+        <v>0.0034</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1208</v>
+        <v>0.0034</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.0569</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1208</v>
+        <v>0.0034</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6052</v>
+        <v>0.0034</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.0569</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="L30" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4517</v>
+        <v>0.0034</v>
       </c>
       <c r="N30" t="n">
-        <v>297</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>STYKO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.0247</v>
+        <v>0.0016</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0073</v>
+        <v>0.0005</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6354</v>
+        <v>-0.6051</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0247</v>
+        <v>0.0016</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0247</v>
+        <v>1.0433</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-1.0417</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0247</v>
+        <v>1.0433</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0247</v>
+        <v>0.5858</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-1.0417</v>
       </c>
       <c r="K31" t="n">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.0247</v>
+        <v>-0.4559000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>89</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1039</v>
+        <v>-0.1259</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0309</v>
+        <v>-0.0374</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6715</v>
+        <v>-0.6631</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1039</v>
+        <v>-0.1259</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1039</v>
+        <v>-0.1259</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1039</v>
+        <v>-0.1259</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1039</v>
+        <v>-0.1259</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1039</v>
+        <v>-0.1259</v>
       </c>
       <c r="N32" t="n">
         <v>72</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1314</v>
+        <v>-0.1262</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.039</v>
+        <v>-0.0375</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.6633</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1314</v>
+        <v>-0.1262</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1314</v>
+        <v>-0.1262</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1314</v>
+        <v>-0.1262</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1314</v>
+        <v>-0.1262</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1314</v>
+        <v>-0.1262</v>
       </c>
       <c r="N33" t="n">
         <v>72</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1345</v>
+        <v>-0.1363</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0399</v>
+        <v>-0.0405</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6854</v>
+        <v>-0.6679</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1345</v>
+        <v>-0.1363</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1345</v>
+        <v>-0.1363</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1345</v>
+        <v>-0.1363</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1345</v>
+        <v>-0.1363</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1345</v>
+        <v>-0.1363</v>
       </c>
       <c r="N34" t="n">
         <v>84</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4206</v>
+        <v>-0.4536</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1249</v>
+        <v>-0.1347</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8157</v>
+        <v>-0.8124</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4206</v>
+        <v>-0.4536</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4206</v>
+        <v>-0.4536</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4206</v>
+        <v>-0.4536</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4206</v>
+        <v>-0.4536</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4206</v>
+        <v>-0.4536</v>
       </c>
       <c r="N35" t="n">
         <v>72</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.5375</v>
+        <v>-0.4957</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1596</v>
+        <v>-0.1472</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8689</v>
+        <v>-0.8316</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.5375</v>
+        <v>-0.4957</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5375</v>
+        <v>-0.4957</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.5375</v>
+        <v>-0.4957</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5375</v>
+        <v>-0.4957</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.5375</v>
+        <v>-0.4957</v>
       </c>
       <c r="N36" t="n">
         <v>134</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7304</v>
+        <v>-0.6745</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2169</v>
+        <v>-0.2003</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9567</v>
+        <v>-0.9131</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7304</v>
+        <v>-0.6745</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7304</v>
+        <v>-0.6745</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7304</v>
+        <v>-0.6745</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7304</v>
+        <v>-0.6745</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7304</v>
+        <v>-0.6745</v>
       </c>
       <c r="N37" t="n">
         <v>84</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9589</v>
+        <v>-0.7645</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2848</v>
+        <v>-0.227</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0607</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9589</v>
+        <v>-0.7645</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.6747</v>
+        <v>-2.4456</v>
       </c>
       <c r="G38" t="n">
-        <v>1.7158</v>
+        <v>1.6811</v>
       </c>
       <c r="H38" t="n">
-        <v>-2.6747</v>
+        <v>-2.4456</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4443</v>
+        <v>-1.3731</v>
       </c>
       <c r="J38" t="n">
-        <v>1.7158</v>
+        <v>1.6811</v>
       </c>
       <c r="K38" t="n">
         <v>108</v>
@@ -2185,7 +2185,7 @@
         <v>156</v>
       </c>
       <c r="M38" t="n">
-        <v>0.2715000000000001</v>
+        <v>0.3080000000000001</v>
       </c>
       <c r="N38" t="n">
         <v>264</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0163</v>
+        <v>-0.9675</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3018</v>
+        <v>-0.2873</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0868</v>
+        <v>-1.0465</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0163</v>
+        <v>-0.9675</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.0163</v>
+        <v>-1.2781</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.3106</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.0163</v>
+        <v>-1.2781</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.0163</v>
+        <v>-0.7176</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.3106</v>
       </c>
       <c r="K39" t="n">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0163</v>
+        <v>-0.407</v>
       </c>
       <c r="N39" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.0356</v>
+        <v>-0.9921</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3076</v>
+        <v>-0.2946</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.0956</v>
+        <v>-1.0577</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.0356</v>
+        <v>-0.9921</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4378</v>
+        <v>-0.9921</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4022</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4378</v>
+        <v>-0.9921</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7764</v>
+        <v>-0.9921</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4022</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>56</v>
+        <v>134</v>
       </c>
       <c r="L40" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.3742</v>
+        <v>-0.9921</v>
       </c>
       <c r="N40" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.3012</v>
+        <v>-1.2968</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3864</v>
+        <v>-0.3851</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.2165</v>
+        <v>-1.1965</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3012</v>
+        <v>-1.2968</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.3012</v>
+        <v>-1.2968</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3012</v>
+        <v>-1.2968</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3012</v>
+        <v>-1.2968</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3012</v>
+        <v>-1.2968</v>
       </c>
       <c r="N41" t="n">
         <v>72</v>
@@ -2429,10 +2429,10 @@
         <v>1.43</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5665</v>
+        <v>0.4962</v>
       </c>
       <c r="J2" t="n">
-        <v>16.995</v>
+        <v>14.886</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.26</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3775</v>
+        <v>0.3159</v>
       </c>
       <c r="J3" t="n">
-        <v>11.325</v>
+        <v>9.477</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.18</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2812</v>
+        <v>0.2286</v>
       </c>
       <c r="J4" t="n">
-        <v>8.436</v>
+        <v>6.858</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0835</v>
+        <v>0.0612</v>
       </c>
       <c r="J5" t="n">
-        <v>2.505</v>
+        <v>1.836</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.67</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3843</v>
+        <v>-0.3738</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.529</v>
+        <v>-11.214</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.3</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4692</v>
+        <v>0.4751</v>
       </c>
       <c r="J7" t="n">
-        <v>14.076</v>
+        <v>14.253</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2434</v>
+        <v>0.2281</v>
       </c>
       <c r="J8" t="n">
-        <v>7.302</v>
+        <v>6.843</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.98</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0423</v>
+        <v>-0.0322</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.269</v>
+        <v>-0.966</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.83</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2217</v>
+        <v>-0.2011</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.651</v>
+        <v>-6.033</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.73</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3193</v>
+        <v>-0.3025</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.579000000000001</v>
+        <v>-9.074999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2345</v>
+        <v>0.1896</v>
       </c>
       <c r="J12" t="n">
-        <v>9.380000000000001</v>
+        <v>7.584</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.07</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1932</v>
+        <v>0.1529</v>
       </c>
       <c r="J13" t="n">
-        <v>7.728</v>
+        <v>6.116</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0007</v>
+        <v>0.0003</v>
       </c>
       <c r="J14" t="n">
-        <v>0.028</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.95</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0853</v>
+        <v>-0.0698</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.412</v>
+        <v>-2.792</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.211</v>
+        <v>-0.1904</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.44</v>
+        <v>-7.616</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.33</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8227</v>
+        <v>0.7986</v>
       </c>
       <c r="J17" t="n">
-        <v>32.908</v>
+        <v>31.944</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.3</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7617</v>
+        <v>0.7336</v>
       </c>
       <c r="J18" t="n">
-        <v>30.468</v>
+        <v>29.344</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3169</v>
+        <v>0.2827</v>
       </c>
       <c r="J19" t="n">
-        <v>12.676</v>
+        <v>11.308</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.09</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2906</v>
+        <v>0.2574</v>
       </c>
       <c r="J20" t="n">
-        <v>11.624</v>
+        <v>10.296</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.164</v>
+        <v>-0.1324</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.56</v>
+        <v>-5.296</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.58</v>
       </c>
       <c r="I22" t="n">
-        <v>0.9967</v>
+        <v>0.9578</v>
       </c>
       <c r="J22" t="n">
-        <v>35.8812</v>
+        <v>34.4808</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.12</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2836</v>
+        <v>0.2351</v>
       </c>
       <c r="J23" t="n">
-        <v>10.2096</v>
+        <v>8.4636</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.99</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.028</v>
+        <v>-0.0199</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.008</v>
+        <v>-0.7164</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.82</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2361</v>
+        <v>-0.2159</v>
       </c>
       <c r="J25" t="n">
-        <v>-8.499599999999999</v>
+        <v>-7.7724</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3513</v>
+        <v>-0.3371</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.6468</v>
+        <v>-12.1356</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.173</v>
+        <v>1.1868</v>
       </c>
       <c r="J27" t="n">
-        <v>42.228</v>
+        <v>42.7248</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.32</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8177</v>
+        <v>0.7925</v>
       </c>
       <c r="J28" t="n">
-        <v>29.4372</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.99</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-0.0552</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.7144</v>
+        <v>-1.9872</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2494</v>
+        <v>-0.2106</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.978400000000001</v>
+        <v>-7.5816</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7201</v>
+        <v>-0.6902</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.9236</v>
+        <v>-24.8472</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5881</v>
+        <v>0.5747</v>
       </c>
       <c r="J32" t="n">
-        <v>13.5263</v>
+        <v>13.2181</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.77</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2602</v>
+        <v>-0.2436</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.9846</v>
+        <v>-5.6028</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.75</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2783</v>
+        <v>-0.2618</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.4009</v>
+        <v>-6.0214</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.58</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4322</v>
+        <v>-0.4235</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.9406</v>
+        <v>-9.740500000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.48</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.5211</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.9531</v>
+        <v>-11.9853</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>2.16</v>
       </c>
       <c r="I37" t="n">
-        <v>1.748</v>
+        <v>1.7971</v>
       </c>
       <c r="J37" t="n">
-        <v>40.204</v>
+        <v>41.3333</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.43</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8381</v>
+        <v>0.8255</v>
       </c>
       <c r="J38" t="n">
-        <v>19.2763</v>
+        <v>18.9865</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.17</v>
       </c>
       <c r="I39" t="n">
-        <v>0.453</v>
+        <v>0.4283</v>
       </c>
       <c r="J39" t="n">
-        <v>10.419</v>
+        <v>9.850899999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.09</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2613</v>
+        <v>0.2302</v>
       </c>
       <c r="J40" t="n">
-        <v>6.0099</v>
+        <v>5.2946</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.84</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5533</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.7259</v>
+        <v>-11.9531</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2391</v>
+        <v>0.1946</v>
       </c>
       <c r="J42" t="n">
-        <v>6.4557</v>
+        <v>5.2542</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.0766</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.4381</v>
+        <v>-2.0682</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.92</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1151</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>-3.1077</v>
+        <v>-2.6892</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.74</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2988</v>
+        <v>-0.2808</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.067600000000001</v>
+        <v>-7.5816</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.72</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3176</v>
+        <v>-0.3004</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.575200000000001</v>
+        <v>-8.110799999999999</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.42</v>
       </c>
       <c r="I47" t="n">
-        <v>0.841</v>
+        <v>0.8258</v>
       </c>
       <c r="J47" t="n">
-        <v>22.707</v>
+        <v>22.2966</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.29</v>
       </c>
       <c r="I48" t="n">
-        <v>0.653</v>
+        <v>0.6414</v>
       </c>
       <c r="J48" t="n">
-        <v>17.631</v>
+        <v>17.3178</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.25</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5927</v>
+        <v>0.5841</v>
       </c>
       <c r="J49" t="n">
-        <v>16.0029</v>
+        <v>15.7707</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.11</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3321</v>
+        <v>0.2994</v>
       </c>
       <c r="J50" t="n">
-        <v>8.966699999999999</v>
+        <v>8.0838</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1654</v>
+        <v>0.1394</v>
       </c>
       <c r="J51" t="n">
-        <v>4.4658</v>
+        <v>3.7638</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1338</v>
+        <v>0.1011</v>
       </c>
       <c r="J52" t="n">
-        <v>3.7464</v>
+        <v>2.8308</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1087</v>
+        <v>0.0801</v>
       </c>
       <c r="J53" t="n">
-        <v>3.0436</v>
+        <v>2.2428</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.92</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.1192</v>
+        <v>-0.1019</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.3376</v>
+        <v>-2.8532</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.91</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1309</v>
+        <v>-0.1128</v>
       </c>
       <c r="J55" t="n">
-        <v>-3.6652</v>
+        <v>-3.1584</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.82</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2272</v>
+        <v>-0.2069</v>
       </c>
       <c r="J56" t="n">
-        <v>-6.3616</v>
+        <v>-5.7932</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.64</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1563</v>
+        <v>1.1525</v>
       </c>
       <c r="J57" t="n">
-        <v>32.3764</v>
+        <v>32.27</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.21</v>
       </c>
       <c r="I58" t="n">
-        <v>0.537</v>
+        <v>0.5279</v>
       </c>
       <c r="J58" t="n">
-        <v>15.036</v>
+        <v>14.7812</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.08</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2633</v>
+        <v>0.2313</v>
       </c>
       <c r="J59" t="n">
-        <v>7.3724</v>
+        <v>6.4764</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.0265</v>
+        <v>-0.021</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.742</v>
+        <v>-0.588</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4506</v>
+        <v>-0.4091</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.6168</v>
+        <v>-11.4548</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.63</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6653</v>
+        <v>0.6224</v>
       </c>
       <c r="J62" t="n">
-        <v>15.3019</v>
+        <v>14.3152</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.51</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5778</v>
+        <v>0.5423</v>
       </c>
       <c r="J63" t="n">
-        <v>13.2894</v>
+        <v>12.4729</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.16</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2461</v>
+        <v>0.2008</v>
       </c>
       <c r="J64" t="n">
-        <v>5.6603</v>
+        <v>4.6184</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.05</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0878</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>2.0194</v>
+        <v>1.4881</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.93</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1318</v>
+        <v>-0.1139</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.0314</v>
+        <v>-2.6197</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.98</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0177</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.4071</v>
+        <v>-0.2277</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.97</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.034</v>
+        <v>-0.0244</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.782</v>
+        <v>-0.5612</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.84</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1932</v>
+        <v>-0.1769</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.4436</v>
+        <v>-4.0687</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.72</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3074</v>
+        <v>-0.2909</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.0702</v>
+        <v>-6.6907</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.41</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5812</v>
+        <v>-0.5921</v>
       </c>
       <c r="J71" t="n">
-        <v>-13.3676</v>
+        <v>-13.6183</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.06</v>
       </c>
       <c r="I72" t="n">
-        <v>0.2057</v>
+        <v>0.1658</v>
       </c>
       <c r="J72" t="n">
-        <v>5.1425</v>
+        <v>4.145</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.01</v>
       </c>
       <c r="I73" t="n">
-        <v>0.0731</v>
+        <v>0.0538</v>
       </c>
       <c r="J73" t="n">
-        <v>1.8275</v>
+        <v>1.345</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>0.8</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.2376</v>
+        <v>-0.2189</v>
       </c>
       <c r="J74" t="n">
-        <v>-5.94</v>
+        <v>-5.4725</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.74</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2951</v>
+        <v>-0.2772</v>
       </c>
       <c r="J75" t="n">
-        <v>-7.3775</v>
+        <v>-6.93</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.61</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4138</v>
+        <v>-0.4037</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.345</v>
+        <v>-10.0925</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.56</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0425</v>
+        <v>1.0318</v>
       </c>
       <c r="J77" t="n">
-        <v>26.0625</v>
+        <v>25.795</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.23</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5575</v>
       </c>
       <c r="J78" t="n">
-        <v>14.15</v>
+        <v>13.9375</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.11</v>
       </c>
       <c r="I79" t="n">
-        <v>0.3385</v>
+        <v>0.3046</v>
       </c>
       <c r="J79" t="n">
-        <v>8.4625</v>
+        <v>7.615</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1069</v>
+        <v>0.0863</v>
       </c>
       <c r="J80" t="n">
-        <v>2.6725</v>
+        <v>2.1575</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.99</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.0906</v>
+        <v>-0.0696</v>
       </c>
       <c r="J81" t="n">
-        <v>-2.265</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.8</v>
       </c>
       <c r="I82" t="n">
-        <v>1.4577</v>
+        <v>1.4863</v>
       </c>
       <c r="J82" t="n">
-        <v>34.9848</v>
+        <v>35.6712</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.78</v>
       </c>
       <c r="I83" t="n">
-        <v>1.433</v>
+        <v>1.46</v>
       </c>
       <c r="J83" t="n">
-        <v>34.392</v>
+        <v>35.04</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.52</v>
       </c>
       <c r="I84" t="n">
-        <v>1.1023</v>
+        <v>1.1158</v>
       </c>
       <c r="J84" t="n">
-        <v>26.4552</v>
+        <v>26.7792</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.87</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4837</v>
+        <v>-0.4485</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.6088</v>
+        <v>-10.764</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.85</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5329</v>
+        <v>-0.4993</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.7896</v>
+        <v>-11.9832</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>0.87</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.1452</v>
+        <v>-0.1291</v>
       </c>
       <c r="J87" t="n">
-        <v>-3.4848</v>
+        <v>-3.0984</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.82</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.2004</v>
+        <v>-0.1851</v>
       </c>
       <c r="J88" t="n">
-        <v>-4.8096</v>
+        <v>-4.4424</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.76</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2615</v>
+        <v>-0.2473</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.276</v>
+        <v>-5.9352</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.63</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3784</v>
+        <v>-0.3665</v>
       </c>
       <c r="J90" t="n">
-        <v>-9.0816</v>
+        <v>-8.795999999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.39</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.589</v>
+        <v>-0.5999</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.136</v>
+        <v>-14.3976</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.51</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1206</v>
+        <v>1.1328</v>
       </c>
       <c r="J92" t="n">
-        <v>30.2562</v>
+        <v>30.5856</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.23</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6103</v>
+        <v>0.5767</v>
       </c>
       <c r="J93" t="n">
-        <v>16.4781</v>
+        <v>15.5709</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.15</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4352</v>
+        <v>0.4001</v>
       </c>
       <c r="J94" t="n">
-        <v>11.7504</v>
+        <v>10.8027</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.04</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1399</v>
+        <v>0.1161</v>
       </c>
       <c r="J95" t="n">
-        <v>3.7773</v>
+        <v>3.1347</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>1.01</v>
       </c>
       <c r="I96" t="n">
-        <v>0.0284</v>
+        <v>0.0185</v>
       </c>
       <c r="J96" t="n">
-        <v>0.7668</v>
+        <v>0.4995</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.29</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5972</v>
+        <v>0.5401</v>
       </c>
       <c r="J97" t="n">
-        <v>16.1244</v>
+        <v>14.5827</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.1</v>
       </c>
       <c r="I98" t="n">
-        <v>0.263</v>
+        <v>0.2152</v>
       </c>
       <c r="J98" t="n">
-        <v>7.101</v>
+        <v>5.8104</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.92</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1195</v>
+        <v>-0.1021</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.2265</v>
+        <v>-2.7567</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.87</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1756</v>
+        <v>-0.1556</v>
       </c>
       <c r="J100" t="n">
-        <v>-4.7412</v>
+        <v>-4.2012</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4677</v>
+        <v>-0.4644</v>
       </c>
       <c r="J101" t="n">
-        <v>-12.6279</v>
+        <v>-12.5388</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.11</v>
       </c>
       <c r="I102" t="n">
-        <v>0.345</v>
+        <v>0.3025</v>
       </c>
       <c r="J102" t="n">
-        <v>7.935</v>
+        <v>6.9575</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.95</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0593</v>
+        <v>-0.0469</v>
       </c>
       <c r="J103" t="n">
-        <v>-1.3639</v>
+        <v>-1.0787</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.88</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.1466</v>
+        <v>-0.1312</v>
       </c>
       <c r="J104" t="n">
-        <v>-3.3718</v>
+        <v>-3.0176</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.47</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5275</v>
+        <v>-0.5299</v>
       </c>
       <c r="J105" t="n">
-        <v>-12.1325</v>
+        <v>-12.1877</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.4</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5876</v>
+        <v>-0.5992</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.5148</v>
+        <v>-13.7816</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.71</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3373</v>
+        <v>1.3589</v>
       </c>
       <c r="J107" t="n">
-        <v>30.7579</v>
+        <v>31.2547</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.67</v>
       </c>
       <c r="I108" t="n">
-        <v>1.2874</v>
+        <v>1.3068</v>
       </c>
       <c r="J108" t="n">
-        <v>29.6102</v>
+        <v>30.0564</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.5</v>
       </c>
       <c r="I109" t="n">
-        <v>1.0699</v>
+        <v>1.0826</v>
       </c>
       <c r="J109" t="n">
-        <v>24.6077</v>
+        <v>24.8998</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.23</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5812</v>
+        <v>0.5552</v>
       </c>
       <c r="J110" t="n">
-        <v>13.3676</v>
+        <v>12.7696</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.95</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2712</v>
+        <v>-0.2396</v>
       </c>
       <c r="J111" t="n">
-        <v>-6.2376</v>
+        <v>-5.5108</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7375</v>
+        <v>0.6829</v>
       </c>
       <c r="J112" t="n">
-        <v>20.65</v>
+        <v>19.1212</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.07</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1922</v>
+        <v>0.1522</v>
       </c>
       <c r="J113" t="n">
-        <v>5.3816</v>
+        <v>4.2616</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.01</v>
       </c>
       <c r="I114" t="n">
-        <v>0.0437</v>
+        <v>0.0295</v>
       </c>
       <c r="J114" t="n">
-        <v>1.2236</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.83</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2218</v>
+        <v>-0.2013</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.2104</v>
+        <v>-5.6364</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.68</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.3656</v>
+        <v>-0.3522</v>
       </c>
       <c r="J116" t="n">
-        <v>-10.2368</v>
+        <v>-9.861599999999999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.35</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8617</v>
+        <v>0.8407</v>
       </c>
       <c r="J117" t="n">
-        <v>24.1276</v>
+        <v>23.5396</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.25</v>
       </c>
       <c r="I118" t="n">
-        <v>0.657</v>
+        <v>0.6237</v>
       </c>
       <c r="J118" t="n">
-        <v>18.396</v>
+        <v>17.4636</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5496</v>
+        <v>0.5135</v>
       </c>
       <c r="J119" t="n">
-        <v>15.3888</v>
+        <v>14.378</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.03</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1108</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="J120" t="n">
-        <v>3.1024</v>
+        <v>2.5172</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.98</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1281</v>
+        <v>-0.1008</v>
       </c>
       <c r="J121" t="n">
-        <v>-3.5868</v>
+        <v>-2.8224</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.23</v>
       </c>
       <c r="I122" t="n">
-        <v>0.6544</v>
+        <v>0.6183</v>
       </c>
       <c r="J122" t="n">
-        <v>19.632</v>
+        <v>18.549</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.22</v>
       </c>
       <c r="I123" t="n">
-        <v>0.6319</v>
+        <v>0.5946</v>
       </c>
       <c r="J123" t="n">
-        <v>18.957</v>
+        <v>17.838</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.95</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.201</v>
+        <v>-0.1664</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.03</v>
+        <v>-4.992</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4451</v>
+        <v>-0.4022</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.353</v>
+        <v>-12.066</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.76</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.679</v>
+        <v>-0.6445</v>
       </c>
       <c r="J126" t="n">
-        <v>-20.37</v>
+        <v>-19.335</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.24</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4899</v>
+        <v>0.4308</v>
       </c>
       <c r="J127" t="n">
-        <v>14.697</v>
+        <v>12.924</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2642</v>
+        <v>0.2176</v>
       </c>
       <c r="J128" t="n">
-        <v>7.926</v>
+        <v>6.528</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.05</v>
       </c>
       <c r="I129" t="n">
-        <v>0.1426</v>
+        <v>0.1108</v>
       </c>
       <c r="J129" t="n">
-        <v>4.278</v>
+        <v>3.324</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.99</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0283</v>
+        <v>-0.0201</v>
       </c>
       <c r="J130" t="n">
-        <v>-0.849</v>
+        <v>-0.603</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.84</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.216</v>
+        <v>-0.1954</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.48</v>
+        <v>-5.862</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.29</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7439</v>
+        <v>0.7144</v>
       </c>
       <c r="J132" t="n">
-        <v>19.3414</v>
+        <v>18.5744</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.24</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6389</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="J133" t="n">
-        <v>16.6114</v>
+        <v>15.7118</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.21</v>
       </c>
       <c r="I134" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.5376</v>
       </c>
       <c r="J134" t="n">
-        <v>14.9266</v>
+        <v>13.9776</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2088</v>
+        <v>0.1795</v>
       </c>
       <c r="J135" t="n">
-        <v>5.4288</v>
+        <v>4.667</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.93</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2874</v>
+        <v>-0.2473</v>
       </c>
       <c r="J136" t="n">
-        <v>-7.4724</v>
+        <v>-6.4298</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.16</v>
       </c>
       <c r="I137" t="n">
-        <v>0.379</v>
+        <v>0.3242</v>
       </c>
       <c r="J137" t="n">
-        <v>9.853999999999999</v>
+        <v>8.4292</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.13</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3235</v>
+        <v>0.2715</v>
       </c>
       <c r="J138" t="n">
-        <v>8.411</v>
+        <v>7.059</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.87</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1747</v>
+        <v>-0.1549</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.5422</v>
+        <v>-4.0274</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2266</v>
+        <v>-0.2064</v>
       </c>
       <c r="J140" t="n">
-        <v>-5.8916</v>
+        <v>-5.3664</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3327</v>
+        <v>-0.3165</v>
       </c>
       <c r="J141" t="n">
-        <v>-8.6502</v>
+        <v>-8.228999999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.19</v>
       </c>
       <c r="I142" t="n">
-        <v>0.446</v>
+        <v>0.3908</v>
       </c>
       <c r="J142" t="n">
-        <v>11.15</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.02</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0917</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>2.2925</v>
+        <v>1.665</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.85</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.192</v>
+        <v>-0.1726</v>
       </c>
       <c r="J144" t="n">
-        <v>-4.8</v>
+        <v>-4.315</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.8</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2424</v>
+        <v>-0.2227</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.06</v>
+        <v>-5.5675</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.61</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4189</v>
+        <v>-0.4096</v>
       </c>
       <c r="J146" t="n">
-        <v>-10.4725</v>
+        <v>-10.24</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.6</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2468</v>
+        <v>1.2647</v>
       </c>
       <c r="J147" t="n">
-        <v>31.17</v>
+        <v>31.6175</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.24</v>
       </c>
       <c r="I148" t="n">
-        <v>0.634</v>
+        <v>0.6004</v>
       </c>
       <c r="J148" t="n">
-        <v>15.85</v>
+        <v>15.01</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.13</v>
       </c>
       <c r="I149" t="n">
-        <v>0.3899</v>
+        <v>0.3545</v>
       </c>
       <c r="J149" t="n">
-        <v>9.7475</v>
+        <v>8.862500000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.07</v>
       </c>
       <c r="I150" t="n">
-        <v>0.2334</v>
+        <v>0.2031</v>
       </c>
       <c r="J150" t="n">
-        <v>5.835</v>
+        <v>5.0775</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.82</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5741000000000001</v>
+        <v>-0.5369</v>
       </c>
       <c r="J151" t="n">
-        <v>-14.3525</v>
+        <v>-13.4225</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.99</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0076</v>
+        <v>0.0162</v>
       </c>
       <c r="J152" t="n">
-        <v>0.1444</v>
+        <v>0.3078</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0737</v>
+        <v>-0.0607</v>
       </c>
       <c r="J153" t="n">
-        <v>-1.4003</v>
+        <v>-1.1533</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.79</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2413</v>
+        <v>-0.2249</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.5847</v>
+        <v>-4.2731</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.64</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3782</v>
+        <v>-0.3652</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.1858</v>
+        <v>-6.9388</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.47</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5279</v>
+        <v>-0.5304</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.0301</v>
+        <v>-10.0776</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.57</v>
       </c>
       <c r="I157" t="n">
-        <v>1.1626</v>
+        <v>1.1781</v>
       </c>
       <c r="J157" t="n">
-        <v>22.0894</v>
+        <v>22.3839</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.43</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9678</v>
+        <v>0.9667</v>
       </c>
       <c r="J158" t="n">
-        <v>18.3882</v>
+        <v>18.3673</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.37</v>
       </c>
       <c r="I159" t="n">
-        <v>0.8623</v>
+        <v>0.8514</v>
       </c>
       <c r="J159" t="n">
-        <v>16.3837</v>
+        <v>16.1766</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.34</v>
       </c>
       <c r="I160" t="n">
-        <v>0.8057</v>
+        <v>0.7912</v>
       </c>
       <c r="J160" t="n">
-        <v>15.3083</v>
+        <v>15.0328</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.28</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6874</v>
+        <v>0.6662</v>
       </c>
       <c r="J161" t="n">
-        <v>13.0606</v>
+        <v>12.6578</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.78</v>
       </c>
       <c r="I162" t="n">
-        <v>1.4607</v>
+        <v>1.4916</v>
       </c>
       <c r="J162" t="n">
-        <v>42.3603</v>
+        <v>43.2564</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.3</v>
       </c>
       <c r="I163" t="n">
-        <v>0.7448</v>
+        <v>0.7194</v>
       </c>
       <c r="J163" t="n">
-        <v>21.5992</v>
+        <v>20.8626</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.21</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5616</v>
+        <v>0.5302</v>
       </c>
       <c r="J164" t="n">
-        <v>16.2864</v>
+        <v>15.3758</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.15</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4264</v>
+        <v>0.3935</v>
       </c>
       <c r="J165" t="n">
-        <v>12.3656</v>
+        <v>11.4115</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.8</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6332</v>
+        <v>-0.6011</v>
       </c>
       <c r="J166" t="n">
-        <v>-18.3628</v>
+        <v>-17.4319</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.99</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.0068</v>
+        <v>-0.0025</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.1972</v>
+        <v>-0.0725</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.86</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1768</v>
+        <v>-0.1598</v>
       </c>
       <c r="J168" t="n">
-        <v>-5.1272</v>
+        <v>-4.6342</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.85</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1872</v>
+        <v>-0.1699</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.4288</v>
+        <v>-4.9271</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.76</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2743</v>
+        <v>-0.2562</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.9547</v>
+        <v>-7.4298</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.67</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3579</v>
+        <v>-0.3432</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.3791</v>
+        <v>-9.9528</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>2.07</v>
       </c>
       <c r="I172" t="n">
-        <v>1.8379</v>
+        <v>1.9148</v>
       </c>
       <c r="J172" t="n">
-        <v>51.4612</v>
+        <v>53.6144</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.11</v>
       </c>
       <c r="I173" t="n">
-        <v>0.3366</v>
+        <v>0.3031</v>
       </c>
       <c r="J173" t="n">
-        <v>9.424799999999999</v>
+        <v>8.486800000000001</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.06</v>
       </c>
       <c r="I174" t="n">
-        <v>0.2004</v>
+        <v>0.1722</v>
       </c>
       <c r="J174" t="n">
-        <v>5.6112</v>
+        <v>4.8216</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.98</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.1342</v>
+        <v>-0.107</v>
       </c>
       <c r="J175" t="n">
-        <v>-3.7576</v>
+        <v>-2.996</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.76</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7147</v>
+        <v>-0.6869</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.0116</v>
+        <v>-19.2332</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.2</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4631</v>
+        <v>0.4075</v>
       </c>
       <c r="J177" t="n">
-        <v>12.9668</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.97</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.0505</v>
+        <v>-0.0407</v>
       </c>
       <c r="J178" t="n">
-        <v>-1.414</v>
+        <v>-1.1396</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.86</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1817</v>
+        <v>-0.1626</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.0876</v>
+        <v>-4.5528</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.83</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2126</v>
+        <v>-0.1929</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.9528</v>
+        <v>-5.4012</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.62</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4102</v>
+        <v>-0.4001</v>
       </c>
       <c r="J181" t="n">
-        <v>-11.4856</v>
+        <v>-11.2028</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2744</v>
+        <v>0.2264</v>
       </c>
       <c r="J182" t="n">
-        <v>7.4088</v>
+        <v>6.1128</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.92</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.1169</v>
+        <v>-0.1008</v>
       </c>
       <c r="J183" t="n">
-        <v>-3.1563</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1394</v>
+        <v>-0.1219</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.7638</v>
+        <v>-3.2913</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.84</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2029</v>
+        <v>-0.1832</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.4783</v>
+        <v>-4.9464</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.75</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.2916</v>
+        <v>-0.2732</v>
       </c>
       <c r="J186" t="n">
-        <v>-7.8732</v>
+        <v>-7.3764</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.49</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0808</v>
+        <v>1.0906</v>
       </c>
       <c r="J187" t="n">
-        <v>29.1816</v>
+        <v>29.4462</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.34</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8236</v>
+        <v>0.8027</v>
       </c>
       <c r="J188" t="n">
-        <v>22.2372</v>
+        <v>21.6729</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.23</v>
       </c>
       <c r="I189" t="n">
-        <v>0.6039</v>
+        <v>0.5734</v>
       </c>
       <c r="J189" t="n">
-        <v>16.3053</v>
+        <v>15.4818</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.2</v>
       </c>
       <c r="I190" t="n">
-        <v>0.5399</v>
+        <v>0.5081</v>
       </c>
       <c r="J190" t="n">
-        <v>14.5773</v>
+        <v>13.7187</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.98</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.1432</v>
+        <v>-0.1165</v>
       </c>
       <c r="J191" t="n">
-        <v>-3.8664</v>
+        <v>-3.1455</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>2.15</v>
       </c>
       <c r="I192" t="n">
-        <v>1.8277</v>
+        <v>1.8876</v>
       </c>
       <c r="J192" t="n">
-        <v>32.8986</v>
+        <v>33.9768</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.54</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1097</v>
+        <v>1.1294</v>
       </c>
       <c r="J193" t="n">
-        <v>19.9746</v>
+        <v>20.3292</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.51</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0717</v>
+        <v>1.0899</v>
       </c>
       <c r="J194" t="n">
-        <v>19.2906</v>
+        <v>19.6182</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.38</v>
       </c>
       <c r="I195" t="n">
-        <v>0.8613</v>
+        <v>0.8558</v>
       </c>
       <c r="J195" t="n">
-        <v>15.5034</v>
+        <v>15.4044</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.21</v>
       </c>
       <c r="I196" t="n">
-        <v>0.5171</v>
+        <v>0.4886</v>
       </c>
       <c r="J196" t="n">
-        <v>9.3078</v>
+        <v>8.7948</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.02</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2312</v>
+        <v>0.2356</v>
       </c>
       <c r="J197" t="n">
-        <v>4.1616</v>
+        <v>4.2408</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.82</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.174</v>
+        <v>-0.1546</v>
       </c>
       <c r="J198" t="n">
-        <v>-3.132</v>
+        <v>-2.7828</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.55</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4347</v>
+        <v>-0.4284</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.8246</v>
+        <v>-7.7112</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.41</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5577</v>
+        <v>-0.5626</v>
       </c>
       <c r="J200" t="n">
-        <v>-10.0386</v>
+        <v>-10.1268</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.14</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7964</v>
+        <v>-0.8495</v>
       </c>
       <c r="J201" t="n">
-        <v>-14.3352</v>
+        <v>-15.291</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.85</v>
       </c>
       <c r="I202" t="n">
-        <v>1.4862</v>
+        <v>1.5174</v>
       </c>
       <c r="J202" t="n">
-        <v>29.724</v>
+        <v>30.348</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.5</v>
       </c>
       <c r="I203" t="n">
-        <v>1.0601</v>
+        <v>1.0767</v>
       </c>
       <c r="J203" t="n">
-        <v>21.202</v>
+        <v>21.534</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.47</v>
       </c>
       <c r="I204" t="n">
-        <v>1.0183</v>
+        <v>1.0302</v>
       </c>
       <c r="J204" t="n">
-        <v>20.366</v>
+        <v>20.604</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.46</v>
       </c>
       <c r="I205" t="n">
-        <v>1.0032</v>
+        <v>1.0132</v>
       </c>
       <c r="J205" t="n">
-        <v>20.064</v>
+        <v>20.264</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.41</v>
       </c>
       <c r="I206" t="n">
-        <v>0.9195</v>
+        <v>0.9187</v>
       </c>
       <c r="J206" t="n">
-        <v>18.39</v>
+        <v>18.374</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.92</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0594</v>
+        <v>-0.0364</v>
       </c>
       <c r="J207" t="n">
-        <v>-1.188</v>
+        <v>-0.728</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.76</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2451</v>
+        <v>-0.2309</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.902</v>
+        <v>-4.618</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.67</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.3336</v>
+        <v>-0.3235</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.672</v>
+        <v>-6.47</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.42</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5521</v>
+        <v>-0.5564</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.042</v>
+        <v>-11.128</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.28</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6753</v>
+        <v>-0.7005</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.506</v>
+        <v>-14.01</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.73</v>
       </c>
       <c r="I212" t="n">
-        <v>1.4008</v>
+        <v>1.4273</v>
       </c>
       <c r="J212" t="n">
-        <v>39.2224</v>
+        <v>39.9644</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.53</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1379</v>
+        <v>1.1506</v>
       </c>
       <c r="J213" t="n">
-        <v>31.8612</v>
+        <v>32.2168</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.08</v>
       </c>
       <c r="I214" t="n">
-        <v>0.251</v>
+        <v>0.2205</v>
       </c>
       <c r="J214" t="n">
-        <v>7.028</v>
+        <v>6.174</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.99</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0993</v>
+        <v>-0.0786</v>
       </c>
       <c r="J215" t="n">
-        <v>-2.7804</v>
+        <v>-2.2008</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5372</v>
+        <v>-0.4999</v>
       </c>
       <c r="J216" t="n">
-        <v>-15.0416</v>
+        <v>-13.9972</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.23</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5194</v>
+        <v>0.4645</v>
       </c>
       <c r="J217" t="n">
-        <v>14.5432</v>
+        <v>13.006</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.15</v>
       </c>
       <c r="I218" t="n">
-        <v>0.3765</v>
+        <v>0.3234</v>
       </c>
       <c r="J218" t="n">
-        <v>10.542</v>
+        <v>9.055199999999999</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.89</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1494</v>
+        <v>-0.1318</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.1832</v>
+        <v>-3.6904</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.73</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3086</v>
+        <v>-0.291</v>
       </c>
       <c r="J220" t="n">
-        <v>-8.6408</v>
+        <v>-8.148</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.42</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5813</v>
+        <v>-0.5938</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.2764</v>
+        <v>-16.6264</v>
       </c>
     </row>
   </sheetData>
